--- a/docs/testcases/manzil-api-testcases.xlsx
+++ b/docs/testcases/manzil-api-testcases.xlsx
@@ -1328,7 +1328,7 @@
       <c r="I12" s="3" t="inlineStr"/>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>api|negative|rbac</t>
+          <t>api|negative|rbac (→ MNZL-269: после промоута на staging expected 403→200)</t>
         </is>
       </c>
     </row>

--- a/docs/testcases/manzil-api-testcases.xlsx
+++ b/docs/testcases/manzil-api-testcases.xlsx
@@ -6989,7 +6989,7 @@
       <c r="I11" s="3" t="inlineStr"/>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>api|positive|pagination</t>
+          <t>api|positive|pagination (→ MNZL-245: dev — вложенный page; при промоуте обновить expected)</t>
         </is>
       </c>
     </row>
@@ -7085,7 +7085,7 @@
       <c r="I13" s="3" t="inlineStr"/>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>api|pagination</t>
+          <t>api|pagination (→ MNZL-245: dev — вложенный page; при промоуте обновить expected)</t>
         </is>
       </c>
     </row>
@@ -7181,7 +7181,7 @@
       <c r="I15" s="3" t="inlineStr"/>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>api|pagination</t>
+          <t>api|pagination (→ MNZL-245: dev — вложенный page; при промоуте обновить expected)</t>
         </is>
       </c>
     </row>
@@ -8193,7 +8193,7 @@
       <c r="I36" s="3" t="inlineStr"/>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>api|positive|pagination</t>
+          <t>api|positive|pagination (→ MNZL-245: dev — вложенный page; при промоуте обновить expected)</t>
         </is>
       </c>
     </row>
@@ -9395,7 +9395,7 @@
       <c r="I61" s="3" t="inlineStr"/>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>api|positive|pagination</t>
+          <t>api|positive|pagination (→ MNZL-245: dev — вложенный page; при промоуте обновить expected)</t>
         </is>
       </c>
     </row>
@@ -9923,7 +9923,7 @@
       <c r="I72" s="3" t="inlineStr"/>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>api|positive|pagination</t>
+          <t>api|positive|pagination (→ MNZL-245: dev — вложенный page; при промоуте обновить expected)</t>
         </is>
       </c>
     </row>
@@ -10888,7 +10888,7 @@
       <c r="I92" s="3" t="inlineStr"/>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>api|positive|pagination</t>
+          <t>api|positive|pagination (→ MNZL-245: dev — вложенный page; при промоуте обновить expected)</t>
         </is>
       </c>
     </row>
@@ -11032,7 +11032,7 @@
       <c r="I95" s="3" t="inlineStr"/>
       <c r="J95" s="2" t="inlineStr">
         <is>
-          <t>api|positive|pagination</t>
+          <t>api|positive|pagination (→ MNZL-245: dev — вложенный page; при промоуте обновить expected)</t>
         </is>
       </c>
     </row>
@@ -11080,7 +11080,7 @@
       <c r="I96" s="3" t="inlineStr"/>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>api|validation</t>
+          <t>api|validation (→ MNZL-245: dev — вложенный page; при промоуте обновить expected)</t>
         </is>
       </c>
     </row>
@@ -11128,7 +11128,7 @@
       <c r="I97" s="3" t="inlineStr"/>
       <c r="J97" s="2" t="inlineStr">
         <is>
-          <t>api|pagination</t>
+          <t>api|pagination (→ MNZL-245: dev — вложенный page; при промоуте обновить expected)</t>
         </is>
       </c>
     </row>
@@ -11789,7 +11789,7 @@
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>HTTP 201, в ответе allCities=true. Переданные cityIds сохраняются как есть, но при isAll=true система считает, что компания работает во всех городах — список городов её не ограничивает.</t>
+          <t>HTTP 201, в ответе isAll=true. Переданные cityIds сохраняются как есть, но при isAll=true система считает, что компания работает во всех городах — список городов её не ограничивает.</t>
         </is>
       </c>
       <c r="H111" s="9" t="inlineStr">
@@ -11800,7 +11800,7 @@
       <c r="I111" s="3" t="inlineStr"/>
       <c r="J111" s="2" t="inlineStr">
         <is>
-          <t>api|positive</t>
+          <t>api|positive (→ MNZL-245: dev — вложенный page; при промоуте обновить expected) · уточнено по фактическому контракту 2026-07-22</t>
         </is>
       </c>
     </row>
@@ -11837,7 +11837,7 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>HTTP 201. Значения по умолчанию: active=true, allCities=false.</t>
+          <t>HTTP 201. Значения по умолчанию: active=true, isAll=false.</t>
         </is>
       </c>
       <c r="H112" s="9" t="inlineStr">
@@ -11848,7 +11848,7 @@
       <c r="I112" s="3" t="inlineStr"/>
       <c r="J112" s="2" t="inlineStr">
         <is>
-          <t>api|positive|boundary</t>
+          <t>api|positive|boundary · уточнено по фактическому контракту 2026-07-22</t>
         </is>
       </c>
     </row>
@@ -12187,7 +12187,7 @@
       <c r="I119" s="3" t="inlineStr"/>
       <c r="J119" s="2" t="inlineStr">
         <is>
-          <t>api|positive|pagination</t>
+          <t>api|positive|pagination (→ MNZL-245: dev — вложенный page; при промоуте обновить expected)</t>
         </is>
       </c>
     </row>
@@ -12283,7 +12283,7 @@
       <c r="I121" s="3" t="inlineStr"/>
       <c r="J121" s="2" t="inlineStr">
         <is>
-          <t>api|positive|pagination</t>
+          <t>api|positive|pagination (→ MNZL-245: dev — вложенный page; при промоуте обновить expected)</t>
         </is>
       </c>
     </row>
@@ -13105,7 +13105,7 @@
       <c r="I138" s="3" t="inlineStr"/>
       <c r="J138" s="2" t="inlineStr">
         <is>
-          <t>api|positive|pagination</t>
+          <t>api|positive|pagination (→ MNZL-245: dev — вложенный page; при промоуте обновить expected)</t>
         </is>
       </c>
     </row>
@@ -13201,7 +13201,7 @@
       <c r="I140" s="3" t="inlineStr"/>
       <c r="J140" s="2" t="inlineStr">
         <is>
-          <t>api|positive|pagination</t>
+          <t>api|positive|pagination (→ MNZL-245: dev — вложенный page; при промоуте обновить expected)</t>
         </is>
       </c>
     </row>
@@ -13249,7 +13249,7 @@
       <c r="I141" s="3" t="inlineStr"/>
       <c r="J141" s="2" t="inlineStr">
         <is>
-          <t>api|pagination</t>
+          <t>api|pagination (→ MNZL-245: dev — вложенный page; при промоуте обновить expected)</t>
         </is>
       </c>
     </row>
@@ -14248,7 +14248,7 @@
       </c>
       <c r="G162" s="2" t="inlineStr">
         <is>
-          <t>HTTP 401 Unauthorized, в теле code="error.unauthorized" — запрос без токена отклоняется ещё до проверки роли, данные не возвращаются.</t>
+          <t>HTTP 401 Unauthorized, в теле code="UNAUTHORIZED" — запрос без токена отклоняется ещё до проверки роли, данные не возвращаются.</t>
         </is>
       </c>
       <c r="H162" s="8" t="inlineStr">
@@ -14259,7 +14259,7 @@
       <c r="I162" s="3" t="inlineStr"/>
       <c r="J162" s="2" t="inlineStr">
         <is>
-          <t>api|rbac</t>
+          <t>api|rbac · уточнено по фактическому контракту 2026-07-22: no-token entry-point даёт UNAUTHORIZED консистентно на всех surface'ах (как AUTH-079); error.unauthorized — доменный 401 при инвалидированном токене</t>
         </is>
       </c>
     </row>

--- a/docs/testcases/manzil-api-testcases.xlsx
+++ b/docs/testcases/manzil-api-testcases.xlsx
@@ -11704,7 +11704,7 @@
       <c r="I109" s="3" t="inlineStr"/>
       <c r="J109" s="2" t="inlineStr">
         <is>
-          <t>api|conflict</t>
+          <t>api|conflict · автоматизировано 2026-07-22: order-lifecycle хелпер (активный заказ → 409 has-active-orders)</t>
         </is>
       </c>
     </row>
@@ -12716,7 +12716,7 @@
       <c r="I130" s="3" t="inlineStr"/>
       <c r="J130" s="2" t="inlineStr">
         <is>
-          <t>api|conflict</t>
+          <t>api|conflict · автоматизировано 2026-07-22: order-lifecycle хелпер (активный заказ → 409 has-active-orders)</t>
         </is>
       </c>
     </row>
@@ -15191,7 +15191,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>HTTP 401; Content-Type: application/problem+json; в теле code='error.unauthorized'.</t>
+          <t>HTTP 401; Content-Type: application/problem+json; в теле code='UNAUTHORIZED'.</t>
         </is>
       </c>
       <c r="H14" s="8" t="inlineStr">
@@ -15202,7 +15202,7 @@
       <c r="I14" s="3" t="inlineStr"/>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>api|rbac</t>
+          <t>api|rbac · уточнено по фактическому контракту 2026-07-22: no-token entry-point даёт UNAUTHORIZED консистентно на всех surface'ах (как AUTH-079)</t>
         </is>
       </c>
     </row>
@@ -15720,7 +15720,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>HTTP 400, code='error.staff.locations-warehouse-only': списки разрешённых складов можно задавать только сотруднику с ролью SHIPPER_WAREHOUSE.</t>
+          <t>HTTP 400, code='error.staff.locations-order-entry-only': списки разрешённых складов можно задавать сотруднику с ORDER_ENTRY: роль SHIPPER_WAREHOUSE или офисная роль с правом ORDER_ENTRY.</t>
         </is>
       </c>
       <c r="H25" s="8" t="inlineStr">
@@ -15731,7 +15731,7 @@
       <c r="I25" s="3" t="inlineStr"/>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>api|negative</t>
+          <t>api|negative · уточнено по фактическому контракту 2026-07-22: код переименован в locations-order-entry-only; правило расширено на роли с ORDER_ENTRY</t>
         </is>
       </c>
     </row>
@@ -16152,7 +16152,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>HTTP 400, code='error.staff.locations-warehouse-only': разрешённые склады задаются только для роли SHIPPER_WAREHOUSE.</t>
+          <t>HTTP 400, code='error.staff.locations-order-entry-only': разрешённые склады задаются для роли с ORDER_ENTRY (SHIPPER_WAREHOUSE или офисная с грантом).</t>
         </is>
       </c>
       <c r="H34" s="9" t="inlineStr">
@@ -16163,7 +16163,7 @@
       <c r="I34" s="3" t="inlineStr"/>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>api|negative</t>
+          <t>api|negative · уточнено по фактическому контракту 2026-07-22: код locations-order-entry-only; правило по ORDER_ENTRY</t>
         </is>
       </c>
     </row>
@@ -16585,7 +16585,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>HTTP 200. Страница заказов: по умолчанию size=10, сортировка createdAt,desc, номер страницы (page) нумеруется с 1. Черновики (DRAFT) и запланированные заказы в списке видны; заказы в статусе SUPERSEDED скрыты. В каждой строке заполнены offerCount (число офферов) и creatorName (кто создал заказ).</t>
+          <t>HTTP 200. Страница заказов: по умолчанию size=10, сортировка createdAt,desc, номер страницы (page) нумеруется с 1. Черновики (DRAFT) и запланированные заказы в списке видны; заказы в статусе SUPERSEDED скрыты. В каждой строке заполнены offerCount (число офферов) и createdByName (кто создал заказ).</t>
         </is>
       </c>
       <c r="H43" s="8" t="inlineStr">
@@ -16596,7 +16596,7 @@
       <c r="I43" s="3" t="inlineStr"/>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>api|positive</t>
+          <t>api|positive · уточнено по факту 2026-07-22: поле списка называется createdByName</t>
         </is>
       </c>
     </row>
@@ -17257,7 +17257,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>HTTP 401; в теле code='error.unauthorized'.</t>
+          <t>HTTP 401; в теле code='UNAUTHORIZED'.</t>
         </is>
       </c>
       <c r="H57" s="9" t="inlineStr">
@@ -17268,7 +17268,7 @@
       <c r="I57" s="3" t="inlineStr"/>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>api|rbac</t>
+          <t>api|rbac · уточнено 2026-07-22: no-token entry-point → UNAUTHORIZED</t>
         </is>
       </c>
     </row>
@@ -18421,7 +18421,7 @@
       <c r="I81" s="3" t="inlineStr"/>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>api|lifecycle</t>
+          <t>api|lifecycle · (→ BUG-035) impl периодически отдаёт 500 вместо 409 (гонка @Version без пессимистичного лока); автотест xfail(strict) с 2026-07-22</t>
         </is>
       </c>
     </row>
@@ -19421,7 +19421,7 @@
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>HTTP 400, code='error.bad-request': значение status вне списка допустимых — тело запроса отклоняется как некорректное.</t>
+          <t>HTTP 400, code='BAD_REQUEST': значение status вне списка допустимых — тело запроса отклоняется как некорректное.</t>
         </is>
       </c>
       <c r="H102" s="10" t="inlineStr">
@@ -19432,7 +19432,7 @@
       <c r="I102" s="3" t="inlineStr"/>
       <c r="J102" s="2" t="inlineStr">
         <is>
-          <t>api|validation</t>
+          <t>api|validation · уточнено 2026-07-22: framework-level 400 (парс/отсутствие параметра) → code BAD_REQUEST, не error.bad-request</t>
         </is>
       </c>
     </row>
@@ -20153,7 +20153,7 @@
       <c r="I117" s="3" t="inlineStr"/>
       <c r="J117" s="2" t="inlineStr">
         <is>
-          <t>api|lifecycle</t>
+          <t>api|lifecycle · (→ BUG-035) impl периодически отдаёт 500 вместо 409 (гонка @Version без пессимистичного лока); автотест xfail(strict) с 2026-07-22</t>
         </is>
       </c>
     </row>
@@ -20719,7 +20719,7 @@
       </c>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>HTTP 400, code='error.bad-request': отсутствует обязательный query-параметр tab.</t>
+          <t>HTTP 400, code='BAD_REQUEST': отсутствует обязательный query-параметр tab.</t>
         </is>
       </c>
       <c r="H129" s="9" t="inlineStr">
@@ -20730,7 +20730,7 @@
       <c r="I129" s="3" t="inlineStr"/>
       <c r="J129" s="2" t="inlineStr">
         <is>
-          <t>api|validation</t>
+          <t>api|validation · уточнено 2026-07-22: framework-level 400 (парс/отсутствие параметра) → code BAD_REQUEST, не error.bad-request</t>
         </is>
       </c>
     </row>
@@ -20767,7 +20767,7 @@
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>HTTP 400, code='error.bad-request': значение tab вне списка допустимых (CONFIRMED, IN_TRANSIT, ENTERED_1C).</t>
+          <t>HTTP 400, code='BAD_REQUEST': значение tab вне списка допустимых (CONFIRMED, IN_TRANSIT, ENTERED_1C).</t>
         </is>
       </c>
       <c r="H130" s="10" t="inlineStr">
@@ -20778,7 +20778,7 @@
       <c r="I130" s="3" t="inlineStr"/>
       <c r="J130" s="2" t="inlineStr">
         <is>
-          <t>api|validation</t>
+          <t>api|validation · уточнено 2026-07-22: framework-level 400 (парс/отсутствие параметра) → code BAD_REQUEST, не error.bad-request</t>
         </is>
       </c>
     </row>
@@ -22112,7 +22112,7 @@
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>HTTP 404: склад ищется только среди складов своей компании — чужой склад не редактируется и отдаётся как несуществующий.</t>
+          <t>HTTP 403, code='error.forbidden': склад ищется только среди складов своей компании — чужой склад не редактируется и отдаётся как несуществующий. (→ BUG-036: непоследовательная стратегия — orders/staff отдают 404, склады 403.)</t>
         </is>
       </c>
       <c r="H158" s="8" t="inlineStr">
@@ -22123,7 +22123,7 @@
       <c r="I158" s="3" t="inlineStr"/>
       <c r="J158" s="2" t="inlineStr">
         <is>
-          <t>api|tenancy</t>
+          <t>api|tenancy · факт: 403 error.forbidden (→ BUG-036: непоследовательное сокрытие кросс-тенанта, решение за продуктом)</t>
         </is>
       </c>
     </row>
@@ -22304,7 +22304,7 @@
       </c>
       <c r="G162" s="2" t="inlineStr">
         <is>
-          <t>HTTP 404: чужой склад не удаляется и отдаётся как несуществующий.</t>
+          <t>HTTP 403, code='error.forbidden': чужой склад не удаляется и отдаётся как несуществующий. (→ BUG-036: непоследовательная стратегия — orders/staff отдают 404, склады 403.)</t>
         </is>
       </c>
       <c r="H162" s="8" t="inlineStr">
@@ -22315,7 +22315,7 @@
       <c r="I162" s="3" t="inlineStr"/>
       <c r="J162" s="2" t="inlineStr">
         <is>
-          <t>api|tenancy</t>
+          <t>api|tenancy · факт: 403 error.forbidden (→ BUG-036: непоследовательное сокрытие кросс-тенанта, решение за продуктом)</t>
         </is>
       </c>
     </row>
@@ -23323,7 +23323,7 @@
       <c r="I183" s="3" t="inlineStr"/>
       <c r="J183" s="2" t="inlineStr">
         <is>
-          <t>api|negative</t>
+          <t>api|negative · automation:backend 2026-07-22: офисная роль без shipperCompanyId недостижима чёрным ящиком (staff всегда с компанией)</t>
         </is>
       </c>
     </row>

--- a/docs/testcases/manzil-api-testcases.xlsx
+++ b/docs/testcases/manzil-api-testcases.xlsx
@@ -18421,7 +18421,7 @@
       <c r="I81" s="3" t="inlineStr"/>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>api|lifecycle · (→ BUG-035) impl периодически отдаёт 500 вместо 409 (гонка @Version без пессимистичного лока); автотест xfail(strict) с 2026-07-22</t>
+          <t>api|lifecycle · (→ BUG-035 / MNZL-275) impl периодически отдаёт 500 вместо 409 (гонка @Version без пессимистичного лока); автотест xfail(strict) с 2026-07-22</t>
         </is>
       </c>
     </row>
@@ -20153,7 +20153,7 @@
       <c r="I117" s="3" t="inlineStr"/>
       <c r="J117" s="2" t="inlineStr">
         <is>
-          <t>api|lifecycle · (→ BUG-035) impl периодически отдаёт 500 вместо 409 (гонка @Version без пессимистичного лока); автотест xfail(strict) с 2026-07-22</t>
+          <t>api|lifecycle · (→ BUG-035 / MNZL-275) impl периодически отдаёт 500 вместо 409 (гонка @Version без пессимистичного лока); автотест xfail(strict) с 2026-07-22</t>
         </is>
       </c>
     </row>
@@ -22112,7 +22112,7 @@
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>HTTP 403, code='error.forbidden': склад ищется только среди складов своей компании — чужой склад не редактируется и отдаётся как несуществующий. (→ BUG-036: непоследовательная стратегия — orders/staff отдают 404, склады 403.)</t>
+          <t>HTTP 403, code='error.forbidden': склад ищется только среди складов своей компании — чужой склад не редактируется и отдаётся как несуществующий. (→ BUG-036 / MNZL-276: непоследовательная стратегия — orders/staff отдают 404, склады 403.)</t>
         </is>
       </c>
       <c r="H158" s="8" t="inlineStr">
@@ -22123,7 +22123,7 @@
       <c r="I158" s="3" t="inlineStr"/>
       <c r="J158" s="2" t="inlineStr">
         <is>
-          <t>api|tenancy · факт: 403 error.forbidden (→ BUG-036: непоследовательное сокрытие кросс-тенанта, решение за продуктом)</t>
+          <t>api|tenancy · факт: 403 error.forbidden (→ BUG-036 / MNZL-276: непоследовательное сокрытие кросс-тенанта, решение за продуктом)</t>
         </is>
       </c>
     </row>
@@ -22304,7 +22304,7 @@
       </c>
       <c r="G162" s="2" t="inlineStr">
         <is>
-          <t>HTTP 403, code='error.forbidden': чужой склад не удаляется и отдаётся как несуществующий. (→ BUG-036: непоследовательная стратегия — orders/staff отдают 404, склады 403.)</t>
+          <t>HTTP 403, code='error.forbidden': чужой склад не удаляется и отдаётся как несуществующий. (→ BUG-036 / MNZL-276: непоследовательная стратегия — orders/staff отдают 404, склады 403.)</t>
         </is>
       </c>
       <c r="H162" s="8" t="inlineStr">
@@ -22315,7 +22315,7 @@
       <c r="I162" s="3" t="inlineStr"/>
       <c r="J162" s="2" t="inlineStr">
         <is>
-          <t>api|tenancy · факт: 403 error.forbidden (→ BUG-036: непоследовательное сокрытие кросс-тенанта, решение за продуктом)</t>
+          <t>api|tenancy · факт: 403 error.forbidden (→ BUG-036 / MNZL-276: непоследовательное сокрытие кросс-тенанта, решение за продуктом)</t>
         </is>
       </c>
     </row>
@@ -25410,7 +25410,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>HTTP 400 Bad Request; в теле code='error.bad-request' — дата принимается только в формате ГГГГ-ММ-ДД.</t>
+          <t>HTTP 400 Bad Request; в теле code='BAD_REQUEST' — дата принимается только в формате ГГГГ-ММ-ДД.</t>
         </is>
       </c>
       <c r="H43" s="10" t="inlineStr">
@@ -25421,7 +25421,7 @@
       <c r="I43" s="3" t="inlineStr"/>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>api|validation</t>
+          <t>api|validation · уточнено 2026-07-22: невалидный формат даты в query → framework BAD_REQUEST (type-mismatch), не error.bad-request</t>
         </is>
       </c>
     </row>
@@ -25593,7 +25593,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Токен TRANSPORT_ADMIN. Заказ вне зоны видимости компании: статус DRAFT, либо город не обслуживается, либо чужой заказ — и ставки по нему у компании нет.</t>
+          <t>Токен TRANSPORT_ADMIN. Заказ в НЕ-marketplace статусе (напр. SELECTED/DRAFT/COMPLETED), по которому у этой компании нет ставки.</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -25603,7 +25603,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>HTTP 404 Not Found; в теле code с текстом «заказ не найден» — недоступный заказ не раскрывается.</t>
+          <t>HTTP 404, code='error.order.not-found'. Видимость detail = статус PUBLISHED/QUOTED (маркетплейс, доступен любому перевозчику) ИЛИ наличие своей ставки; фильтры города/blacklist/exclusion действуют только на ленту-список, не на detail. Заказ вне маркетплейса и без ставки не раскрывается.</t>
         </is>
       </c>
       <c r="H47" s="8" t="inlineStr">
@@ -25614,7 +25614,7 @@
       <c r="I47" s="3" t="inlineStr"/>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>api|tenancy</t>
+          <t>api|tenancy · уточнено по факту 2026-07-22: canView(TRANSPORT)=marketplace-статус ИЛИ hasBid; город/blacklist фильтруют только ленту. Прежняя формулировка «город не обслуживается→404» неверна для detail</t>
         </is>
       </c>
     </row>

--- a/docs/testcases/manzil-api-testcases.xlsx
+++ b/docs/testcases/manzil-api-testcases.xlsx
@@ -10067,7 +10067,7 @@
       <c r="I75" s="3" t="inlineStr"/>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>api|positive</t>
+          <t>api|positive · автоматизировано 2026-07-22: division-склады CN/KG создаются через POST /shipper/warehouses, резолв cityName/country проверен</t>
         </is>
       </c>
     </row>
@@ -25877,12 +25877,12 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Capability: MANAGER БЕЗ гранта TENDER_SELECT → 403 error.forbidden</t>
+          <t>Capability: MANAGER БЕЗ гранта SEE_PRICES → 403 error.forbidden</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>Токен SHIPPER_MANAGER, у пользователя НЕ выдано индивидуальное право TENDER_SELECT. Заказ его компании со ставками.</t>
+          <t>Токен SHIPPER_MANAGER, у пользователя НЕ выдано индивидуальное право SEE_PRICES. Заказ его компании со ставками.</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -25892,7 +25892,7 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>HTTP 403 Forbidden; в теле code='error.forbidden'. Роль проходит проверку, но без права TENDER_SELECT просмотр ставок недоступен.</t>
+          <t>HTTP 403 Forbidden; в теле code='error.forbidden'. Роль проходит проверку, но без права SEE_PRICES просмотр ставок недоступен.</t>
         </is>
       </c>
       <c r="H53" s="8" t="inlineStr">
@@ -25903,7 +25903,7 @@
       <c r="I53" s="3" t="inlineStr"/>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>api|capability|rbac</t>
+          <t>api|capability|rbac · уточнено по факту 2026-07-22: GET offers гейтится SEE_PRICES (список показывает цены конкурентов), TENDER_SELECT нужен только для POST select</t>
         </is>
       </c>
     </row>
@@ -25925,12 +25925,12 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Capability: MANAGER С грантом TENDER_SELECT → 200</t>
+          <t>Capability: MANAGER С грантом SEE_PRICES → 200</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Токен SHIPPER_MANAGER, пользователю выдано индивидуальное право TENDER_SELECT. Заказ его компании со ставками.</t>
+          <t>Токен SHIPPER_MANAGER, пользователю выдано индивидуальное право SEE_PRICES. Заказ его компании со ставками.</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -25940,7 +25940,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>HTTP 200 OK; список ставок возвращается — действующие права пользователя содержат TENDER_SELECT.</t>
+          <t>HTTP 200 OK; список ставок возвращается — действующие права пользователя содержат SEE_PRICES.</t>
         </is>
       </c>
       <c r="H54" s="8" t="inlineStr">
@@ -25951,7 +25951,7 @@
       <c r="I54" s="3" t="inlineStr"/>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>api|capability|rbac</t>
+          <t>api|capability|rbac · уточнено по факту 2026-07-22: GET offers гейтится SEE_PRICES (список показывает цены конкурентов), TENDER_SELECT нужен только для POST select</t>
         </is>
       </c>
     </row>
@@ -25978,7 +25978,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>Токены SHIPPER_OPERATOR и SHIPPER_DISPATCHER без права TENDER_SELECT (в наборах прав по умолчанию этим ролям оно не выдаётся).</t>
+          <t>Токены SHIPPER_OPERATOR и SHIPPER_DISPATCHER без права SEE_PRICES (в наборах прав по умолчанию этим ролям оно не выдаётся).</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -25999,7 +25999,7 @@
       <c r="I55" s="3" t="inlineStr"/>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>api|capability|rbac</t>
+          <t>api|capability|rbac · уточнено по факту 2026-07-22: GET offers гейтится SEE_PRICES (список показывает цены конкурентов), TENDER_SELECT нужен только для POST select</t>
         </is>
       </c>
     </row>
@@ -26336,7 +26336,7 @@
       <c r="I62" s="3" t="inlineStr"/>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>api|negative|lifecycle</t>
+          <t>api|negative|lifecycle · automation:backend 2026-07-22: не-PENDING оффер на QUOTED-заказе недостижим чёрным ящиком (select уводит из QUOTED, republish-REVERT восстанавливает PENDING); порядок проверки offer!=PENDING→not-selectable подтверждён по OfferService Проверяется интеграционным тестом manzil-core: порядок guard'ов в OfferService.selectWinner — status!=QUOTED→error.order.not-selectable ПРЕЖДЕ offer-lookup; offer!=PENDING→error.offer.not-selectable (тот же код, что и невалидный статус заказа). Чёрным ящиком состояние «не-PENDING оффер на QUOTED-заказе» недостижимо.</t>
         </is>
       </c>
     </row>
@@ -27774,7 +27774,7 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>HTTP 200 OK; постраничный ответ: 20 на страницу по умолчанию, новые первыми. У каждого водителя: признак занятости — currentOrderId и отображаемый номер заказа (если занят), а также completedCount (число завершённых заказов). В списке только водители своей компании.</t>
+          <t>HTTP 200 OK; постраничный ответ: 20 на страницу по умолчанию, новые первыми. У каждого водителя: признак занятости — currentOrderId и отображаемый номер заказа (если занят), а также completedOrders (число завершённых заказов). В списке только водители своей компании.</t>
         </is>
       </c>
       <c r="H92" s="8" t="inlineStr">
@@ -27785,7 +27785,7 @@
       <c r="I92" s="3" t="inlineStr"/>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>api|positive</t>
+          <t>api|positive · уточнено по факту 2026-07-22: поле счётчика — completedOrders</t>
         </is>
       </c>
     </row>

--- a/docs/testcases/manzil-api-testcases.xlsx
+++ b/docs/testcases/manzil-api-testcases.xlsx
@@ -32340,7 +32340,7 @@
       <c r="I28" s="3" t="inlineStr"/>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>api|negative|tenancy</t>
+          <t>api|negative|tenancy · уточнено по факту 2026-07-23: 404 требует вызывающего с пустым allowed-списком (admin=все); у роли SHIPPER_WAREHOUSE с непустым allowed случайный id → 403 error.order.warehouse-not-allowed (проверка allowed раньше существования, OrderService L991-999 vs L1191)</t>
         </is>
       </c>
     </row>
@@ -32388,7 +32388,7 @@
       <c r="I29" s="3" t="inlineStr"/>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>api|negative|tenancy</t>
+          <t>api|negative|tenancy · уточнено по факту 2026-07-23: 404 требует вызывающего с пустым allowed-списком (admin=все); у роли SHIPPER_WAREHOUSE с непустым allowed случайный id → 403 error.order.warehouse-not-allowed (проверка allowed раньше существования, OrderService L991-999 vs L1191)</t>
         </is>
       </c>
     </row>
@@ -37203,7 +37203,7 @@
       <c r="I129" s="3" t="inlineStr"/>
       <c r="J129" s="2" t="inlineStr">
         <is>
-          <t>api|capability</t>
+          <t>api|capability · automation:backend 2026-07-23: снятие дефолтного ORDER_REVIEW у офисной роли недостижимо чёрным ящиком (capabilities добавляют гранты, не убирают дефолты)</t>
         </is>
       </c>
     </row>
@@ -37300,7 +37300,7 @@
       <c r="I131" s="3" t="inlineStr"/>
       <c r="J131" s="2" t="inlineStr">
         <is>
-          <t>api|positive</t>
+          <t>api|positive · automation:pending 2026-07-23: нужен хелпер провизининга dispatch/view-событий (агрегация viewCount=max по нескольким строкам получателя) — Фаза 4b integrations</t>
         </is>
       </c>
     </row>
@@ -37349,7 +37349,7 @@
       <c r="I132" s="3" t="inlineStr"/>
       <c r="J132" s="2" t="inlineStr">
         <is>
-          <t>api|positive</t>
+          <t>api|positive · automation:pending 2026-07-23: нужен хелпер провизининга dispatch/view-событий (сортировка TRANSPORT&gt;DRIVER, viewCount desc) — Фаза 4b integrations</t>
         </is>
       </c>
     </row>
@@ -37493,7 +37493,7 @@
       <c r="I135" s="3" t="inlineStr"/>
       <c r="J135" s="2" t="inlineStr">
         <is>
-          <t>api|positive</t>
+          <t>api|positive · automation:pending 2026-07-23: нужен хелпер провизининга dispatch/view-событий (фильтрация удалённого получателя) — Фаза 4b integrations</t>
         </is>
       </c>
     </row>
@@ -37685,7 +37685,7 @@
       <c r="I139" s="3" t="inlineStr"/>
       <c r="J139" s="2" t="inlineStr">
         <is>
-          <t>api|negative|rbac</t>
+          <t>api|negative|rbac · automation:backend 2026-07-23: офисная роль без shipperCompanyId недостижима ЧЯ (staff всегда с компанией) — как SHP-182</t>
         </is>
       </c>
     </row>

--- a/docs/testcases/manzil-api-testcases.xlsx
+++ b/docs/testcases/manzil-api-testcases.xlsx
@@ -37300,7 +37300,7 @@
       <c r="I131" s="3" t="inlineStr"/>
       <c r="J131" s="2" t="inlineStr">
         <is>
-          <t>api|positive · automation:pending 2026-07-23: нужен хелпер провизининга dispatch/view-событий (агрегация viewCount=max по нескольким строкам получателя) — Фаза 4b integrations</t>
+          <t>api|positive · automation:pending 2026-07-23: нужен хелпер провизининга dispatch/view-событий (агрегация viewCount=max по нескольким строкам получателя) — Фаза 4b integrations · закрыто 2026-07-23: view-события (POST /orders/{id}/view) в test_int_notifications.py</t>
         </is>
       </c>
     </row>
@@ -37349,7 +37349,7 @@
       <c r="I132" s="3" t="inlineStr"/>
       <c r="J132" s="2" t="inlineStr">
         <is>
-          <t>api|positive · automation:pending 2026-07-23: нужен хелпер провизининга dispatch/view-событий (сортировка TRANSPORT&gt;DRIVER, viewCount desc) — Фаза 4b integrations</t>
+          <t>api|positive · automation:pending 2026-07-23: нужен хелпер провизининга dispatch/view-событий (сортировка TRANSPORT&gt;DRIVER, viewCount desc) — Фаза 4b integrations · закрыто 2026-07-23: view-события (POST /orders/{id}/view) в test_int_notifications.py</t>
         </is>
       </c>
     </row>
@@ -37493,7 +37493,7 @@
       <c r="I135" s="3" t="inlineStr"/>
       <c r="J135" s="2" t="inlineStr">
         <is>
-          <t>api|positive · automation:pending 2026-07-23: нужен хелпер провизининга dispatch/view-событий (фильтрация удалённого получателя) — Фаза 4b integrations</t>
+          <t>api|positive · automation:pending 2026-07-23: нужен хелпер провизининга dispatch/view-событий (фильтрация удалённого получателя) — Фаза 4b integrations · закрыто 2026-07-23: view-события (POST /orders/{id}/view) в test_int_notifications.py</t>
         </is>
       </c>
     </row>
@@ -39242,7 +39242,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>HTTP 200; в теле поле count — число непрочитанных PUSH-уведомлений пользователя (значение для бейджа).</t>
+          <t>HTTP 200; в теле поле поле unread — число непрочитанных PUSH-уведомлений пользователя (значение для бейджа).</t>
         </is>
       </c>
       <c r="H32" s="9" t="inlineStr">
@@ -39253,7 +39253,7 @@
       <c r="I32" s="3" t="inlineStr"/>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>api|positive</t>
+          <t>api|positive · уточнено 2026-07-23: поле счётчика — unread (не count)</t>
         </is>
       </c>
     </row>
@@ -39483,7 +39483,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>HTTP 400, code=error.bad-request — значение в пути не является корректным UUID.</t>
+          <t>HTTP 400, code=BAD_REQUEST — значение в пути не является корректным UUID.</t>
         </is>
       </c>
       <c r="H37" s="10" t="inlineStr">
@@ -39494,7 +39494,7 @@
       <c r="I37" s="3" t="inlineStr"/>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>api|validation</t>
+          <t>api|validation · уточнено 2026-07-23: невалидный UUID в пути → framework BAD_REQUEST</t>
         </is>
       </c>
     </row>

--- a/docs/testcases/manzil-api-testcases.xlsx
+++ b/docs/testcases/manzil-api-testcases.xlsx
@@ -40821,7 +40821,7 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>Выполнен вход под SHIPPER_ADMIN, у которого нет capability SMS_BLAST.</t>
+          <t>Выполнен вход под SHIPPER_OPERATOR (роль без capability SMS_BLAST по умолчанию); заказ в статусе PUBLISHED.</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
@@ -40842,7 +40842,7 @@
       <c r="I65" s="3" t="inlineStr"/>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>api|capability</t>
+          <t>api|capability · уточнено по факту: SMS_BLAST есть по умолчанию у ADMIN/MANAGER/DISPATCHER — роль без неё это OPERATOR (2026-07-23)</t>
         </is>
       </c>
     </row>
@@ -41398,7 +41398,7 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>Выполнен вход под SHIPPER_ADMIN, у которого нет capability SMS_JOURNAL.</t>
+          <t>Выполнен вход под SHIPPER_OPERATOR (роль без capability SMS_JOURNAL по умолчанию).</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
@@ -41419,7 +41419,7 @@
       <c r="I77" s="3" t="inlineStr"/>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>api|capability</t>
+          <t>api|capability · уточнено по факту: SMS_JOURNAL есть по умолчанию у ADMIN/MANAGER/DISPATCHER — роль без неё это OPERATOR (2026-07-23)</t>
         </is>
       </c>
     </row>

--- a/docs/testcases/manzil-api-testcases.xlsx
+++ b/docs/testcases/manzil-api-testcases.xlsx
@@ -37956,7 +37956,7 @@
       <c r="I5" s="3" t="inlineStr"/>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>api|security</t>
+          <t>api|security · на dev ONEC_WEBHOOK_SECRET пуст → fail-closed: 003…006 наблюдаемо сходятся к 401 error.unauthorized (2026-07-23)</t>
         </is>
       </c>
     </row>
@@ -38052,7 +38052,7 @@
       <c r="I7" s="3" t="inlineStr"/>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>api|security</t>
+          <t>api|security · на dev ONEC_WEBHOOK_SECRET пуст → fail-closed: 003…006 наблюдаемо сходятся к 401 error.unauthorized (2026-07-23)</t>
         </is>
       </c>
     </row>
@@ -38089,7 +38089,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>HTTP 400, code=error.bad-request; в errors указано поле eventId (обязательное, пустое значение не допускается).</t>
+          <t>HTTP 400, code=BAD_REQUEST; в errors указано поле eventId (обязательное, пустое значение не допускается).</t>
         </is>
       </c>
       <c r="H8" s="8" t="inlineStr">
@@ -38100,7 +38100,7 @@
       <c r="I8" s="3" t="inlineStr"/>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>api|validation</t>
+          <t>api|validation · уточнено по факту: bean-валидация даёт code=BAD_REQUEST, не error.bad-request (2026-07-23)</t>
         </is>
       </c>
     </row>
@@ -38137,7 +38137,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>HTTP 400, code=error.bad-request; в errors указано поле licensePlate (обязательное, пустое значение не допускается).</t>
+          <t>HTTP 400, code=BAD_REQUEST; в errors указано поле licensePlate (обязательное, пустое значение не допускается).</t>
         </is>
       </c>
       <c r="H9" s="8" t="inlineStr">
@@ -38148,7 +38148,7 @@
       <c r="I9" s="3" t="inlineStr"/>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>api|validation</t>
+          <t>api|validation · уточнено по факту: code=BAD_REQUEST (2026-07-23)</t>
         </is>
       </c>
     </row>
@@ -38473,7 +38473,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>HTTP 400, code=error.bad-request — некорректный JSON отклоняется, обработка не начинается.</t>
+          <t>HTTP 400, code=BAD_REQUEST — некорректный JSON отклоняется, обработка не начинается.</t>
         </is>
       </c>
       <c r="H16" s="9" t="inlineStr">
@@ -38484,7 +38484,7 @@
       <c r="I16" s="3" t="inlineStr"/>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>api|validation</t>
+          <t>api|validation · уточнено по факту: code=BAD_REQUEST (2026-07-23)</t>
         </is>
       </c>
     </row>
@@ -38666,7 +38666,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>HTTP 400, code=error.bad-request — пустой список items не допускается.</t>
+          <t>HTTP 400, code=BAD_REQUEST — пустой список items не допускается (проверяется ЗА shared-secret; см. BUG-040).</t>
         </is>
       </c>
       <c r="H20" s="9" t="inlineStr">
@@ -38677,7 +38677,7 @@
       <c r="I20" s="3" t="inlineStr"/>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>api|validation</t>
+          <t>api|validation (→ BUG-040) · батч JWT-гейтится → недостижим для 1С; тест xfail(strict) на корректный контракт</t>
         </is>
       </c>
     </row>
@@ -38714,7 +38714,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>HTTP 400; сообщение об ошибке о слишком большом батче — лимит 500 элементов. Ни одно событие из батча не обрабатывается.</t>
+          <t>HTTP 400; сообщение об ошибке о слишком большом батче — лимит 500 элементов, code=BAD_REQUEST. Ни одно событие из батча не обрабатывается (проверка за shared-secret; см. BUG-040).</t>
         </is>
       </c>
       <c r="H21" s="9" t="inlineStr">
@@ -38725,7 +38725,7 @@
       <c r="I21" s="3" t="inlineStr"/>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>api|boundary</t>
+          <t>api|boundary (→ BUG-040) · батч JWT-гейтится → xfail(strict)</t>
         </is>
       </c>
     </row>
@@ -38762,7 +38762,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>HTTP 400, code=error.bad-request — валидация применяется к каждому элементу списка, батч с невалидным элементом отклоняется целиком.</t>
+          <t>HTTP 400, code=BAD_REQUEST — валидация применяется к каждому элементу списка, батч с невалидным элементом отклоняется целиком (за shared-secret; см. BUG-040).</t>
         </is>
       </c>
       <c r="H22" s="9" t="inlineStr">
@@ -38773,7 +38773,7 @@
       <c r="I22" s="3" t="inlineStr"/>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>api|validation</t>
+          <t>api|validation (→ BUG-040) · батч JWT-гейтится → xfail(strict)</t>
         </is>
       </c>
     </row>
@@ -38821,7 +38821,7 @@
       <c r="I23" s="3" t="inlineStr"/>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>api|security</t>
+          <t>api|security (→ BUG-040) · батч без JWT → 401 UNAUTHORIZED (framework) вместо shared-secret 401 error.unauthorized; xfail(strict)</t>
         </is>
       </c>
     </row>

--- a/docs/testcases/manzil-api-testcases.xlsx
+++ b/docs/testcases/manzil-api-testcases.xlsx
@@ -40350,7 +40350,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>HTTP 413, code=error.request.too-large — запрос отклоняется ещё на этапе приёма загрузки.</t>
+          <t>HTTP 413; запрос отклоняется multipart-резолвером ещё на этапе приёма. code=CONTENT_TOO_LARGE (framework-паттерн: у не-доменных ошибок code=имя статуса); доменный текст error.request.too-large локализован в detail/message.</t>
         </is>
       </c>
       <c r="H55" s="9" t="inlineStr">
@@ -40361,7 +40361,7 @@
       <c r="I55" s="3" t="inlineStr"/>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>api|boundary</t>
+          <t>api|boundary · уточнено по факту: framework-413 даёт code=CONTENT_TOO_LARGE, ключ error.request.too-large — только в тексте detail (2026-07-23)</t>
         </is>
       </c>
     </row>

--- a/docs/testcases/manzil-api-testcases.xlsx
+++ b/docs/testcases/manzil-api-testcases.xlsx
@@ -43990,7 +43990,7 @@
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>Водитель не найден</t>
+          <t>Несуществующий driverId → проверка привязки срабатывает раньше lookup</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
@@ -44005,7 +44005,7 @@
       </c>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>HTTP 404, code=error.driver.not-found.</t>
+          <t>HTTP 404, code=error.order.driver-not-attached. Проверка привязки водителя к заказу (existsByOrderIdAndDriverId) выполняется РАНЬШЕ lookup водителя, поэтому неизвестный driverId неотличим от непривязанного. Код error.driver.not-found достижим лишь в orphan-состоянии (водитель привязан, но запись водителя удалена) — чёрным ящиком не воспроизводится.</t>
         </is>
       </c>
       <c r="H131" s="9" t="inlineStr">
@@ -44016,7 +44016,7 @@
       <c r="I131" s="3" t="inlineStr"/>
       <c r="J131" s="2" t="inlineStr">
         <is>
-          <t>api|negative</t>
+          <t>api|negative · уточнено по факту: guard-порядок — driver-not-attached раньше driver.not-found (2026-07-23)</t>
         </is>
       </c>
     </row>
@@ -44283,7 +44283,7 @@
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>Выполнен вход под SHIPPER_ADMIN, у которого нет capability BLACKLIST.</t>
+          <t>Выполнен вход под SHIPPER_OPERATOR (shipper-роль без capability BLACKLIST по умолчанию — BLACKLIST admin-only-grantable, нет в дефолтах ролей). Есть COMPLETED-заказ с привязанным водителем.</t>
         </is>
       </c>
       <c r="F137" s="2" t="inlineStr">
@@ -44304,7 +44304,7 @@
       <c r="I137" s="3" t="inlineStr"/>
       <c r="J137" s="2" t="inlineStr">
         <is>
-          <t>api|capability</t>
+          <t>api|capability · уточнено по факту: BLACKLIST есть только у ADMIN (ADMIN=all); роль без неё — OPERATOR/MANAGER/DISPATCHER (2026-07-23)</t>
         </is>
       </c>
     </row>

--- a/docs/testcases/manzil-api-testcases.xlsx
+++ b/docs/testcases/manzil-api-testcases.xlsx
@@ -47980,7 +47980,7 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>DRIVER не входит ни в один clientType (WEB/WAREHOUSE_APP/TRANSPORT_COMPANY_APP)</t>
+          <t>DRIVER входит только через TRANSPORT_COMPANY_APP; WEB/WAREHOUSE_APP → wrong-app</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -47997,7 +47997,7 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>Во всех трёх случаях — HTTP 403, в теле ответа code='error.wrong-app', токены не выдаются. Вход водителю недоступен ни через один тип клиента (веб, приложение склада, приложение перевозчика): отдельного входа для водителей пока не предусмотрено — это ожидаемое поведение, а не дефект.</t>
+          <t>clientType WEB → HTTP 403 error.wrong-app; WAREHOUSE_APP → HTTP 403 error.wrong-app; TRANSPORT_COMPANY_APP → HTTP 200, выдаётся пара токенов (роль DRIVER, effectiveCapabilities=[]). Вход водителя разрешён через приложение перевозчика.</t>
         </is>
       </c>
       <c r="H58" s="8" t="inlineStr">
@@ -48008,7 +48008,7 @@
       <c r="I58" s="3" t="inlineStr"/>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>security|negative</t>
+          <t>security · уточнено по факту (→ MNZL-269): при промоуте на staging TRANSPORT_COMPANY_APP пускает и DRIVER; прежний expected (wrong-app во всех) устарел (2026-07-23)</t>
         </is>
       </c>
     </row>
@@ -49112,7 +49112,7 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>Смена роли админом отражается в дефолтном наборе capability при следующем токене</t>
+          <t>Смена роли отражается в дефолтном наборе capability немедленно (роль из БД, не из JWT)</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
@@ -49129,7 +49129,7 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>Шаг 3: HTTP 403, code='error.forbidden' — у роли SHIPPER_DISPATCHER права ORDER_ENTRY нет. Роль записана внутрь токена, поэтому смена роли применяется после перевыпуска токена (перелогина) — в отличие от персональных грантов, которые действуют сразу.</t>
+          <t>Шаг 3: HTTP 403, code=error.forbidden — смена роли OPERATOR→DISPATCHER убирает ORDER_ENTRY СРАЗУ, тем же токеном, без релогина. caller.getRole() грузится из БД (@CurrentUser), поэтому capability-дефолты роли живут из БД (как и персональные гранты). Ролевой @PreAuthorize-гейт секции по-прежнему берёт роль из JWT (стал бы актуален после релогина), но проверка права — из БД.</t>
         </is>
       </c>
       <c r="H81" s="9" t="inlineStr">
@@ -49140,7 +49140,7 @@
       <c r="I81" s="3" t="inlineStr"/>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>rbac|capability|security</t>
+          <t>rbac|capability|security · уточнено по факту: роль читается из БД (@CurrentUser) → смена роли мгновенна для capability, релогин НЕ нужен; прежний expected «нужен релогин» неверен (2026-07-23)</t>
         </is>
       </c>
     </row>

--- a/docs/testcases/manzil-api-testcases.xlsx
+++ b/docs/testcases/manzil-api-testcases.xlsx
@@ -38581,7 +38581,7 @@
       <c r="I18" s="3" t="inlineStr"/>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>api|positive</t>
+          <t>api|positive (→ BUG-040) · батч JWT-гейтится (401) — тест xfail(strict) на корректный shared-secret контракт</t>
         </is>
       </c>
     </row>
@@ -38629,7 +38629,7 @@
       <c r="I19" s="3" t="inlineStr"/>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>api|negative</t>
+          <t>api|negative (→ BUG-040) · батч JWT-гейтится (401) — тест xfail(strict) на корректный shared-secret контракт</t>
         </is>
       </c>
     </row>
@@ -38869,7 +38869,7 @@
       <c r="I24" s="3" t="inlineStr"/>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>api|idempotency</t>
+          <t>api|idempotency (→ BUG-040) · батч JWT-гейтится (401) — тест xfail(strict) на корректный shared-secret контракт</t>
         </is>
       </c>
     </row>
@@ -38917,7 +38917,7 @@
       <c r="I25" s="3" t="inlineStr"/>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>api|idempotency</t>
+          <t>api|idempotency (→ BUG-040) · батч JWT-гейтится (401) — тест xfail(strict) на корректный shared-secret контракт</t>
         </is>
       </c>
     </row>

--- a/docs/testcases/manzil-api-testcases.xlsx
+++ b/docs/testcases/manzil-api-testcases.xlsx
@@ -37493,7 +37493,7 @@
       <c r="I135" s="3" t="inlineStr"/>
       <c r="J135" s="2" t="inlineStr">
         <is>
-          <t>api|positive · automation:pending 2026-07-23: нужен хелпер провизининга dispatch/view-событий (фильтрация удалённого получателя) — Фаза 4b integrations · закрыто 2026-07-23: view-события (POST /orders/{id}/view) в test_int_notifications.py</t>
+          <t>api|positive · тест робастен к потоку push-получателей: проверяет исчезновение строки-ПРОСМОТРА удалённого перевозчика</t>
         </is>
       </c>
     </row>
@@ -39050,7 +39050,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>HTTP 200; content=[] (пустой список), totalElements=0.</t>
+          <t>HTTP 200, список уведомлений. Уточнено по факту: bid-request PUSH о новом заказе шлётся ВСЕМ перевозчикам (не только eligible/isAll, в отличие от SMS-рассылки), поэтому у «пассивного» перевозчика журнал не обязан быть пустым — но содержит только broadcast bid-request'ы (каждый привязан к заказу), чужих уведомлений нет.</t>
         </is>
       </c>
       <c r="H28" s="10" t="inlineStr">
@@ -39061,7 +39061,7 @@
       <c r="I28" s="3" t="inlineStr"/>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>api|boundary</t>
+          <t>api|positive · уточнено по факту: PUSH bid-request широковещательный (все перевозчики), тест робастен к потоку (2026-07-24)</t>
         </is>
       </c>
     </row>
@@ -39543,7 +39543,7 @@
       <c r="I38" s="3" t="inlineStr"/>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>api|positive</t>
+          <t>api|positive · тест робастен к параллельному bid-request PUSH: проверяет, что пред-существующие уведомления стали read (не мгновенный unread==0)</t>
         </is>
       </c>
     </row>
@@ -41755,7 +41755,7 @@
       <c r="I84" s="3" t="inlineStr"/>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>api|rbac</t>
+          <t>api|rbac · dev-drift DRIFT-001 (ждём подтверждения): dev отдаёт 200 анонимно; тест xfail(strict) на корректном 401</t>
         </is>
       </c>
     </row>

--- a/docs/testcases/manzil-api-testcases.xlsx
+++ b/docs/testcases/manzil-api-testcases.xlsx
@@ -41729,7 +41729,7 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>Неаутентифицированный доступ</t>
+          <t>Справочники стран/городов ПУБЛИЧНЫ без токена (пред-логинный маркетплейс)</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
@@ -41744,7 +41744,7 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>HTTP 401 — справочник доступен только аутентифицированным пользователям.</t>
+          <t>HTTP 200 — /countries и /cities доступны БЕЗ токена (Driver/ТК листают заказы и фильтруют по стране/городу до авторизации; форма входа всплывает лишь при попытке откликнуться). Граница публичного проходит по странам/городам: divisions (CN/KG) остаются под auth → 401.</t>
         </is>
       </c>
       <c r="H84" s="9" t="inlineStr">
@@ -41755,7 +41755,7 @@
       <c r="I84" s="3" t="inlineStr"/>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>api|rbac · dev-drift DRIFT-001 (ждём подтверждения): dev отдаёт 200 анонимно; тест xfail(strict) на корректном 401</t>
+          <t>api|security · публично по дизайну (→ пред-логинный просмотр маркетплейса, подтверждено разработчиком 2026-07-24); прежний DRIFT-001 закрыт</t>
         </is>
       </c>
     </row>
@@ -49374,7 +49374,7 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>Шаги 1–2: HTTP 200 — справочники доступны. Шаг 3 (без токена): HTTP 401, code='UNAUTHORIZED'.</t>
+          <t>Страны/города (/countries, /cities) — ПУБЛИЧНЫ: читаются и БЕЗ токена (200; пред-логинный просмотр маркетплейса, подтверждено разработчиком 2026-07-24). Административное деление CN/KG (/cn/divisions, /kg/divisions) — под аутентификацией: без токена 401. Аутентифицированная роль читает все справочники.</t>
         </is>
       </c>
       <c r="H86" s="10" t="inlineStr">
@@ -49385,7 +49385,7 @@
       <c r="I86" s="3" t="inlineStr"/>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>rbac|positive</t>
+          <t>rbac|positive · уточнено по факту: countries/cities публичны (пред-логин), divisions под auth (2026-07-24)</t>
         </is>
       </c>
     </row>

--- a/docs/testcases/manzil-api-testcases.xlsx
+++ b/docs/testcases/manzil-api-testcases.xlsx
@@ -15,6 +15,7 @@
     <sheet name="API — Склад+Диспетчер" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="API — Интеграции+SMS" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="API — RBAC" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="API — Регистрация" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -497,7 +498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -710,20 +711,45 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>API — Регистрация/Сброс/Публичное</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>API — Регистрация</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>/auth/register/* (OTP) · /auth/reset/* · transporters/{id}/verification · /public/cargo · публичные справочники</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr"/>
-      <c r="C9" s="5" t="inlineStr"/>
-      <c r="D9" s="6" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr"/>
+      <c r="C10" s="5" t="inlineStr"/>
+      <c r="D10" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
       </c>
-      <c r="E9" s="7" t="n">
-        <v>1008</v>
+      <c r="E10" s="7" t="n">
+        <v>1078</v>
       </c>
     </row>
   </sheetData>
@@ -49881,4 +49907,3485 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J71"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="52" customWidth="1" min="6" max="6"/>
+    <col width="56" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Раздел</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Экран / Подраздел</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Сценарий</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Предусловия</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Шаги</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Ожидаемый результат</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Приоритет</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Статус</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Комментарий</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>API-REG-001</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>API — Регистрация, восстановление пароля, публичная лента</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>POST /api/v1/auth/register/otp</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Запрос OTP на незанятый телефон — happy path</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Выделенный НЕзарегистрированный телефон в формате E.164 (например +998900000000). Эндпойнт публичный — токен не нужен.</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>1. Запрос: POST /api/v1/auth/register/otp с телом {phone:'+998900000000', lang:'ru'} без заголовка Authorization.</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200. В теле: challengeId (UUID) и resendAfter=45 (секунды до разрешённого повтора). На стенде с тестовым OTP-кодом SMS не отправляется — код фиксированный.</t>
+        </is>
+      </c>
+      <c r="H2" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr"/>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>api|positive</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>API-REG-002</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>API — Регистрация, восстановление пароля, публичная лента</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>POST /api/v1/auth/register/otp</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Повторный запрос кода раньше кулдауна 45 с → 429</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Только что (менее 45 с назад) запрошен OTP на выделенный телефон.</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>1. Сразу повторить POST /api/v1/auth/register/otp с тем же phone.</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 429, code='error.otp.resend-too-soon', detail «Код можно запросить повторно позже». Новый challenge не создаётся, счётчик попыток прежнего кода не сбрасывается.</t>
+        </is>
+      </c>
+      <c r="H3" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr"/>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>api|negative|ratelimit</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>API-REG-003</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>API — Регистрация, восстановление пароля, публичная лента</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>POST /api/v1/auth/register/otp</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Повторный запрос после кулдауна: новый challenge, старый аннулирован</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>OTP запрошен более 45 с назад, код не использован.</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1. Повторить POST /api/v1/auth/register/otp с тем же phone.
+2. Попытаться подтвердить СТАРЫЙ challengeId верным кодом: POST /api/v1/auth/register/otp/verify.</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Шаг 1: HTTP 200, выдан НОВЫЙ challengeId. Шаг 2: HTTP 401, code='error.otp.token-invalid' — прежний challenge погашен, живым остаётся только последний код (один живой challenge на телефон+назначение).</t>
+        </is>
+      </c>
+      <c r="H4" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr"/>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>api|negative|lifecycle</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>API-REG-004</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>API — Регистрация, восстановление пароля, публичная лента</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>POST /api/v1/auth/register/otp</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Телефон уже зарегистрирован (активный аккаунт) → 409</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Существует активный пользователь с известным телефоном (любая роль).</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>1. POST /api/v1/auth/register/otp с phone активного пользователя.</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 409, code='error.registration.phone-taken', detail «Этот номер телефона уже зарегистрирован». SMS/challenge не создаются.</t>
+        </is>
+      </c>
+      <c r="H5" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr"/>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>api|negative|conflict</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>API-REG-005</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>API — Регистрация, восстановление пароля, публичная лента</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>POST /api/v1/auth/register/otp</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Телефон заблокированного (деактивированного) пользователя → 409</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Есть пользователь, деактивированный админом (active=false); телефон известен.</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>1. POST /api/v1/auth/register/otp с телефоном заблокированного пользователя.</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 409, code='error.registration.phone-taken' — блокировка не освобождает номер: повторная саморегистрация на занятый номер запрещена в любом состоянии аккаунта.</t>
+        </is>
+      </c>
+      <c r="H6" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr"/>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>api|negative|security</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>API-REG-006</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>API — Регистрация, восстановление пароля, публичная лента</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>POST /api/v1/auth/register/otp</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Телефон удалённого (soft-delete) пользователя → 409, воскрешение запрещено</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Есть пользователь, удалённый через админ-API (soft-delete); телефон известен.</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>1. POST /api/v1/auth/register/otp с телефоном удалённого пользователя.</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 409, code='error.registration.phone-taken'. Саморегистрация не должна «воскрешать» удалённый аккаунт (переиспользовать старый users.id/Keycloak-identity) — удалённого возвращает только админ.</t>
+        </is>
+      </c>
+      <c r="H7" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr"/>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>api|negative|security</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>API-REG-007</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>API — Регистрация, восстановление пароля, публичная лента</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>POST /api/v1/auth/register/otp</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Невалидный формат телефона → 400 с errors[]</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>1. POST /api/v1/auth/register/otp поочерёдно с phone: '998900000000' (без «+»), '+9989ab000000' (буквы), '+998 90 000 00 00' (пробелы).</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Каждый вариант: HTTP 400, в errors[] поле phone с сообщением о неверном формате (шаблон ^\+[0-9]{10,15}$). Challenge не создаётся.</t>
+        </is>
+      </c>
+      <c r="H8" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr"/>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>api|validation</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>API-REG-008</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>API — Регистрация, восстановление пароля, публичная лента</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>POST /api/v1/auth/register/otp</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Телефон отсутствует или пустой → 400</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>1. POST /api/v1/auth/register/otp с телом {} и с {phone:''}.</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 400, в errors[] поле phone с сообщением об обязательности (validation.phoneRequired).</t>
+        </is>
+      </c>
+      <c r="H9" s="10" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr"/>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>api|validation</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>API-REG-009</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>API — Регистрация, восстановление пароля, публичная лента</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>POST /api/v1/auth/register/otp</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Границы длины телефона: 10 и 15 цифр валидны, 9 и 16 — нет</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Выделенные незанятые номера подходящей длины.</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1. POST с phone из «+» и 10 цифр, затем из «+» и 15 цифр.
+2. POST с phone из «+» и 9 цифр, затем из «+» и 16 цифр.</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>Шаг 1: оба запроса HTTP 200 (нижняя и верхняя границы шаблона включительно). Шаг 2: оба HTTP 400 с ошибкой валидации по полю phone.</t>
+        </is>
+      </c>
+      <c r="H10" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr"/>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>api|boundary|validation</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>API-REG-010</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>API — Регистрация, восстановление пароля, публичная лента</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>POST /api/v1/auth/register/otp</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Поле lang необязательное; неизвестное значение не ломает запрос</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Выделенный незанятый телефон.</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>1. POST без поля lang.
+2. POST (после кулдауна/другой номер) с lang:'xx'.</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>Оба запроса HTTP 200 с challengeId — lang лишь подсказка для текста SMS и не валидируется жёстко. (Сейчас SMS в любом случае уходит на узбекском — единственный одобренный шаблон PlayMobile, MNZL-278.)</t>
+        </is>
+      </c>
+      <c r="H11" s="10" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr"/>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>api|validation|i18n</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>API-REG-011</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>API — Регистрация, восстановление пароля, публичная лента</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>POST /api/v1/auth/register/otp</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Пер-IP лимит OTP-запросов: 21-й запрос за 10 минут → 429</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Выделенный пул телефонов (лимит общий на IP для register/otp И reset/otp). Запускать серийно, не на учётках основных прогонов.</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>1. С одного IP выполнить 20 запросов POST /api/v1/auth/register/otp на разные телефоны (уложившись в 10 минут).
+2. Выполнить 21-й запрос.</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>Первые 20 — по контракту (200/409/429-кулдаун). 21-й: HTTP 429, code='error.too-many-attempts' — защита от спрея SMS по многим номерам с одного источника. Окно скользящее 10 минут.</t>
+        </is>
+      </c>
+      <c r="H12" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr"/>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>api|negative|ratelimit|security</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>API-REG-012</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>API — Регистрация, восстановление пароля, публичная лента</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>POST /api/v1/auth/register/otp</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Доставка SMS на +998: PlayMobile, текст на узбекском</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Стенд с реальной отправкой SMS (тестовый OTP-код ВЫКЛЮЧЕН, PlayMobile настроен). Реальный телефон +998 под рукой.</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>1. POST /api/v1/auth/register/otp с реальным +998-номером и lang:'ru'.
+2. Дождаться SMS.</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>SMS приходит через PlayMobile; текст на узбекском независимо от lang (одобрен только узбекский шаблон, MNZL-278). Внутри — 6-значный код.</t>
+        </is>
+      </c>
+      <c r="H13" s="10" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr"/>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>api|i18n|manual</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>API-REG-013</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>API — Регистрация, восстановление пароля, публичная лента</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>POST /api/v1/auth/register/otp</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Доставка SMS на +86: Aliyun, шаблонный OTP</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Стенд с реальной отправкой SMS (Aliyun настроен, шаблон одобрен). Реальный китайский номер +86.</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>1. POST /api/v1/auth/register/otp с реальным +86-номером.
+2. Дождаться SMS.</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>SMS приходит через Aliyun по одобренному OTP-шаблону (в Китае свободный текст запрещён). Внутри — 6-значный код. Сбой доставки не влияет на ответ API (доставка best-effort, challenge остаётся живым и переотправляемым).</t>
+        </is>
+      </c>
+      <c r="H14" s="10" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr"/>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>api|i18n|manual</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>API-REG-014</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>API — Регистрация, восстановление пароля, публичная лента</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>POST /api/v1/auth/register/otp/verify</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Подтверждение верным кодом → registrationToken</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Получен challengeId; код известен (тестовый OTP-код стенда или из SMS).</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>1. POST /api/v1/auth/register/otp/verify с телом {challengeId, code:'&lt;верный 6-значный&gt;'}.</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200. В теле: registrationToken — компактный JWT (три сегмента через точки). Токен короткоживущий (20 минут) и предъявляется на шаге complete.</t>
+        </is>
+      </c>
+      <c r="H15" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr"/>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>api|positive</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>API-REG-015</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>API — Регистрация, восстановление пароля, публичная лента</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>POST /api/v1/auth/register/otp/verify</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Неверный код → 422</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Живой challengeId.</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>1. POST /api/v1/auth/register/otp/verify с заведомо неверным кодом (например '000000', не равным верному).</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 422, code='error.otp.invalid', detail «Неверный код подтверждения». Попытка засчитана в счётчик (максимум 5).</t>
+        </is>
+      </c>
+      <c r="H16" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr"/>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>api|negative</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>API-REG-016</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>API — Регистрация, восстановление пароля, публичная лента</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>POST /api/v1/auth/register/otp/verify</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Верный код после 1–4 неверных попыток проходит</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Живой challengeId, верный код известен.</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>1. Отправить 2 неверных кода (оба → 422).
+2. Отправить верный код.</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>Шаг 2: HTTP 200 с registrationToken — неверные попытки в пределах лимита (5) не блокируют подтверждение верным кодом.</t>
+        </is>
+      </c>
+      <c r="H17" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr"/>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>api|positive|state</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>API-REG-017</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>API — Регистрация, восстановление пароля, публичная лента</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>POST /api/v1/auth/register/otp/verify</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Блокировка после 5 неверных попыток; верный код больше не принимается</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Свежий challengeId, верный код известен.</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>1. Отправить 5 неверных кодов подряд.
+2. Отправить ВЕРНЫЙ код.</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>Попытки 1–4: HTTP 422 error.otp.invalid. Попытка 5: HTTP 429, code='error.otp.locked', detail «Слишком много попыток. Попробуйте позже». Шаг 2 (верный код): тоже HTTP 429 error.otp.locked — challenge заблокирован окончательно, нужен новый запрос кода (после кулдауна). Перезапрос кода НЕ сбрасывает счётчик досрочно (кулдаун 45 с).</t>
+        </is>
+      </c>
+      <c r="H18" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr"/>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>api|negative|security|boundary</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>API-REG-018</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>API — Регистрация, восстановление пароля, публичная лента</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>POST /api/v1/auth/register/otp/verify</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Код истёк (TTL 5 минут) → 410</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Challenge создан более 5 минут назад и не подтверждён. Тест реального времени — запускать отдельно (маркер slow).</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>1. Запросить OTP, подождать более 5 минут.
+2. POST verify с верным кодом.</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 410, code='error.otp.expired', detail «Код подтверждения истёк». Просроченный challenge не мешает запросить новый код.</t>
+        </is>
+      </c>
+      <c r="H19" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr"/>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>api|negative|slow</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>API-REG-019</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>API — Регистрация, восстановление пароля, публичная лента</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>POST /api/v1/auth/register/otp/verify</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Несуществующий challengeId → 401</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>1. POST verify со случайным UUID в challengeId и любым кодом.</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 401, code='error.otp.token-invalid', detail «Недействительный или уже использованный запрос».</t>
+        </is>
+      </c>
+      <c r="H20" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr"/>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>api|negative</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>API-REG-020</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>API — Регистрация, восстановление пароля, публичная лента</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>POST /api/v1/auth/register/otp/verify</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Повторное подтверждение использованного challenge → 401 (одноразовость)</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Challenge успешно подтверждён (registrationToken получен).</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>1. Повторить POST verify с тем же challengeId и тем же верным кодом.</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 401, code='error.otp.token-invalid' — challenge одноразовый: после успешного подтверждения он потреблён, второй registrationToken по нему получить нельзя.</t>
+        </is>
+      </c>
+      <c r="H21" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr"/>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>api|negative|security|idempotency</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>API-REG-021</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>API — Регистрация, восстановление пароля, публичная лента</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>POST /api/v1/auth/register/otp/verify</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Отсутствие challengeId или code → 400</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>1. POST verify с телом {code:'123456'} (без challengeId).
+2. POST verify с телом {challengeId:'&lt;uuid&gt;'} (без code).</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>Оба запроса: HTTP 400 с errors[] по отсутствующему полю (validation.required).</t>
+        </is>
+      </c>
+      <c r="H22" s="10" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr"/>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>api|validation</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>API-REG-022</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>API — Регистрация, восстановление пароля, публичная лента</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>POST /api/v1/auth/register/complete</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Регистрация транспортной компании — happy path с автовходом</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Действующий registrationToken (шаги OTP+verify пройдены). Известны id городов из GET /api/v1/cities.</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>1. POST /api/v1/auth/register/complete с телом {registrationToken, role:'TRANSPORT_COMPANY', password:'&lt;6+ симв&gt;', fullName:'AT-ТК Админ', companyName:'AT-ТК-&lt;uniq&gt;', inn:'123456789', address:'г. Ташкент, ул. Тестовая 1', departureCityIds:[&lt;cityId&gt;]}.
+2. GET /api/v1/me с полученным accessToken.</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>Шаг 1: HTTP 200 — сразу токены входа: accessToken, refreshToken, expiresIn (число секунд), tokenType='Bearer' (автовход, приложение перевозчика фиксируется сервером). Шаг 2: HTTP 200, role='TRANSPORT_ADMIN', verificationStatus='PENDING' — аккаунт создан и ждёт проверки.</t>
+        </is>
+      </c>
+      <c r="H23" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr"/>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>api|positive|lifecycle</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>API-REG-023</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>API — Регистрация, восстановление пароля, публичная лента</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>POST /api/v1/auth/register/complete</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Регистрация самозанятого водителя — happy path</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Действующий registrationToken по другому незанятому телефону.</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>1. POST complete с телом {registrationToken, role:'DRIVER', password:'&lt;6+&gt;', fullName:'AT-Водитель', idCardNumber:'AA1234567'}.
+2. GET /api/v1/me с полученным accessToken.</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>Шаг 1: HTTP 200 с accessToken/refreshToken/expiresIn/tokenType. Шаг 2: role='DRIVER', verificationStatus='PENDING'. Поля ТК (companyName/inn/address/города) для роли DRIVER не требуются.</t>
+        </is>
+      </c>
+      <c r="H24" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr"/>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>api|positive|lifecycle</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>API-REG-024</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>API — Регистрация, восстановление пароля, публичная лента</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>POST /api/v1/auth/register/complete</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Созданная ТК видна супер-админу со статусом «на рассмотрении»</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>Только что зарегистрирована ТК (API-REG-022). Токен SUPER_ADMIN.</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>1. GET /api/v1/super-admin/transport-companies?search=&lt;companyName&gt; под SUPER_ADMIN.</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200, компания найдена: name/tin/address совпадают с введёнными, verificationStatus='PENDING', города отправки сохранены.</t>
+        </is>
+      </c>
+      <c r="H25" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr"/>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>api|positive</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>API-REG-025</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>API — Регистрация, восстановление пароля, публичная лента</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>POST /api/v1/auth/register/complete</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Созданный водитель виден супер-админу: cardId, active, PENDING</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Только что зарегистрирован водитель (API-REG-023). Токен SUPER_ADMIN.</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>1. GET /api/v1/super-admin/self-employed-drivers?search=&lt;fullName или телефон&gt; под SUPER_ADMIN.</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200, водитель найден: verificationStatus='PENDING', номер паспорта/ID (cardId) совпадает с введённым idCardNumber, запись активна. Тип ТС и госномер пустые — заполняются позже.</t>
+        </is>
+      </c>
+      <c r="H26" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr"/>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>api|positive</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>API-REG-026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>API — Регистрация, восстановление пароля, публичная лента</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>POST /api/v1/auth/register/complete</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>Пароль короче 6 символов → 400</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>Действующий registrationToken.</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>1. POST complete с password:'12345' (5 символов), остальные поля валидны.</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 400, в errors[] поле password с сообщением о минимальной длине (validation.passwordMinLength). Аккаунт не создан — токен остаётся пригодным для повторной попытки.</t>
+        </is>
+      </c>
+      <c r="H27" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr"/>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>api|validation|boundary</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>API-REG-027</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>API — Регистрация, восстановление пароля, публичная лента</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>POST /api/v1/auth/register/complete</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>ФИО короче 3 символов или пустое → 400</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>Действующий registrationToken.</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>1. POST complete с fullName:'АБ' (2 символа), остальные поля валидны.</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 400, в errors[] поле fullName (validation.fullNameRequired).</t>
+        </is>
+      </c>
+      <c r="H28" s="10" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr"/>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>api|validation|boundary</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>API-REG-028</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>API — Регистрация, восстановление пароля, публичная лента</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>POST /api/v1/auth/register/complete</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>ТК без companyName → 400 с доменной ошибкой</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>Действующий registrationToken.</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>1. POST complete с role:'TRANSPORT_COMPANY' без поля companyName (или с пустым), остальное валидно.</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 400, code='error.registration.company-name-required', detail «Укажите название компании».</t>
+        </is>
+      </c>
+      <c r="H29" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr"/>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>api|validation</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>API-REG-029</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>API — Регистрация, восстановление пароля, публичная лента</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>POST /api/v1/auth/register/complete</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>ИНН ТК: строго 9 цифр — 8, 10 цифр и буквы отклоняются</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>Действующие registrationToken'ы (или повтор с тем же токеном после 400 — токен не сгорает на ошибке валидации).</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>1. POST complete (role TRANSPORT_COMPANY) поочерёдно с inn:'12345678' (8 цифр), '1234567890' (10 цифр), '12345678a' (буква).
+2. POST с inn:'123456789' (ровно 9 цифр).</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>Шаг 1: каждый вариант HTTP 400, code='error.registration.inn-invalid', detail «ИНН должен состоять из 9 цифр». Шаг 2: проходит дальше (200 при прочих валидных полях).</t>
+        </is>
+      </c>
+      <c r="H30" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr"/>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>api|validation|boundary</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>API-REG-030</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>API — Регистрация, восстановление пароля, публичная лента</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>POST /api/v1/auth/register/complete</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>ТК без адреса → 400</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>Действующий registrationToken.</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>1. POST complete (role TRANSPORT_COMPANY) без поля address (или с пустым/пробельным).</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 400, code='error.registration.address-required', detail «Укажите адрес».</t>
+        </is>
+      </c>
+      <c r="H31" s="10" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="inlineStr"/>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>api|validation</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>API-REG-031</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>API — Регистрация, восстановление пароля, публичная лента</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>POST /api/v1/auth/register/complete</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>ТК без городов отправки → 400</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>Действующий registrationToken.</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>1. POST complete (role TRANSPORT_COMPANY) с departureCityIds:[] и отдельно вовсе без поля.</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>Оба варианта: HTTP 400, code='error.registration.cities-required', detail «Выберите хотя бы один город отправки».</t>
+        </is>
+      </c>
+      <c r="H32" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr"/>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>api|validation</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>API-REG-032</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>API — Регистрация, восстановление пароля, публичная лента</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>POST /api/v1/auth/register/complete</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>Водитель: номер паспорта/ID короче 7 символов → 400</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>Действующий registrationToken.</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>1. POST complete (role DRIVER) с idCardNumber:'AA1234' (6 символов).
+2. POST с idCardNumber из 7 символов.</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>Шаг 1: HTTP 400, code='error.registration.id-card-invalid', detail «Укажите корректный номер паспорта / ID». Шаг 2: граница включительно — 7 символов проходят (200 при прочих валидных полях).</t>
+        </is>
+      </c>
+      <c r="H33" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="inlineStr"/>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>api|validation|boundary</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>API-REG-033</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>API — Регистрация, восстановление пароля, публичная лента</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>POST /api/v1/auth/register/complete</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>role отсутствует или вне справочника → 400</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>Действующий registrationToken.</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>1. POST complete без поля role.
+2. POST complete с role:'SUPER_ADMIN' (недопустимое значение — саморегистрация только TRANSPORT_COMPANY и DRIVER).</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>Оба запроса: HTTP 400 (отсутствие — errors[] validation.required; чужое значение не десериализуется в enum). Зарегистрировать привилегированную роль через публичный эндпойнт невозможно.</t>
+        </is>
+      </c>
+      <c r="H34" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr"/>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>api|validation|security</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>API-REG-034</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>API — Регистрация, восстановление пароля, публичная лента</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>POST /api/v1/auth/register/complete</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>Мусорный/подделанный registrationToken → 401</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>1. POST complete с registrationToken:'abc.def.ghi' (не подписанный сервером JWT), остальные поля валидны.</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 401, code='error.otp.token-invalid'. Токен проверяется по HMAC-подписи сервера — самодельный/чужой токен отклоняется, аккаунт не создаётся.</t>
+        </is>
+      </c>
+      <c r="H35" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I35" s="3" t="inlineStr"/>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>api|negative|security</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>API-REG-035</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>API — Регистрация, восстановление пароля, публичная лента</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>POST /api/v1/auth/register/complete</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>Просроченный registrationToken (старше 20 минут) → 401</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>registrationToken получен более 20 минут назад и не использован. Тест реального времени — запускать отдельно (маркер slow).</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>1. POST complete с этим токеном и валидными полями.</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 401, code='error.otp.token-invalid' — срок действия registration-токена 20 минут; нужно пройти OTP заново.</t>
+        </is>
+      </c>
+      <c r="H36" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr"/>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>api|negative|slow</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>API-REG-036</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>API — Регистрация, восстановление пароля, публичная лента</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>POST /api/v1/auth/register/complete</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>Подмена назначения: reset-токен вместо registration-токена → 401</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>Получен действующий resetToken (через /auth/reset/otp + verify для зарегистрированного телефона).</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>1. POST /api/v1/auth/register/complete, подставив в registrationToken значение resetToken.</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 401, code='error.otp.token-invalid' — токены привязаны к назначению (purpose): токен сброса пароля не годится для регистрации и наоборот.</t>
+        </is>
+      </c>
+      <c r="H37" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I37" s="3" t="inlineStr"/>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>api|negative|security</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>API-REG-037</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>API — Регистрация, восстановление пароля, публичная лента</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>POST /api/v1/auth/register/complete</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Повторный complete с тем же токеном (replay) → 401, дубликат не создаётся</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>Регистрация по токену уже успешно завершена.</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>1. Повторить POST complete с тем же registrationToken (можно с другой ролью/полями).</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 401, code='error.otp.token-invalid' — токен одноразовый: исходный challenge погашен при первом complete. Второй аккаунт не создаётся.</t>
+        </is>
+      </c>
+      <c r="H38" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I38" s="3" t="inlineStr"/>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>api|negative|security|idempotency</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>API-REG-038</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>API — Регистрация, восстановление пароля, публичная лента</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>POST /api/v1/auth/register/complete</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>Телефон занят между verify и complete → 409</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>Действующий registrationToken на телефон X. Токен SUPER_ADMIN для создания пользователя.</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>1. Пока registrationToken жив, создать через админ-API пользователя с телефоном X (например сотрудника).
+2. POST complete с этим registrationToken.</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 409, code='error.registration.phone-taken' — занятость телефона перепроверяется на завершении. Аккаунт/компания не создаются.</t>
+        </is>
+      </c>
+      <c r="H39" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I39" s="3" t="inlineStr"/>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>api|negative|conflict</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>API-REG-039</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>API — Регистрация, восстановление пароля, публичная лента</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>POST /api/v1/auth/login (clientType)</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>Самозарегистрированный водитель (DRIVER) входит в приложение перевозчика</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>Зарегистрирован водитель (PENDING), пароль известен.</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>1. POST /api/v1/auth/login с {phone, password, clientType:'TRANSPORT_COMPANY_APP'}.</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200 с токенами: приложение перевозчика теперь обслуживает и ТК (TRANSPORT_ADMIN), и самозанятого водителя (DRIVER) — обе роли входят в TRANSPORT_COMPANY_APP (новое правило MNZL-269). PENDING-статус входу НЕ мешает.</t>
+        </is>
+      </c>
+      <c r="H40" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I40" s="3" t="inlineStr"/>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>api|positive|rbac</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>API-REG-040</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>API — Регистрация, восстановление пароля, публичная лента</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>POST /api/v1/auth/login (clientType)</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>DRIVER в WEB-консоль → 403 wrong-app</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>Зарегистрирован водитель, пароль известен.</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>1. POST /api/v1/auth/login с {phone, password, clientType:'WEB'}.</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 403, code='error.wrong-app' — роль DRIVER не входит в список ролей веб-консоли; водитель работает только из мобильного приложения перевозчика.</t>
+        </is>
+      </c>
+      <c r="H41" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I41" s="3" t="inlineStr"/>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>api|negative|rbac</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>API-REG-041</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>API — Регистрация, восстановление пароля, публичная лента</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Гейтинг непроверенных (verification_status)</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>PENDING-водитель видит ленту заявок (просмотр без верификации разрешён)</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>Водитель зарегистрирован, статус PENDING; токен получен. На стенде есть опубликованные заказы.</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>1. GET /api/v1/driver/feed под PENDING-водителем.
+2. GET /api/v1/driver/feed/{id} по заказу из ленты.</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>Оба запроса HTTP 200 — непроверенный водитель может осматриваться (лента и деталь), чтобы решить, ждать ли проверки. Ограничены только действия (ставки и далее).</t>
+        </is>
+      </c>
+      <c r="H42" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I42" s="3" t="inlineStr"/>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>api|positive|rbac|state</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>API-REG-042</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>API — Регистрация, восстановление пароля, публичная лента</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>Гейтинг непроверенных (verification_status)</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>PENDING-водитель не может подать ставку → 403 verification-required</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>PENDING-водитель; в ленте есть открытый заказ.</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>1. POST /api/v1/driver/orders/{orderId}/offers с валидным телом ставки под PENDING-водителем.</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 403, code='error.verification-required', detail «Аккаунт на проверке — действие недоступно до подтверждения». Ставка не создаётся.</t>
+        </is>
+      </c>
+      <c r="H43" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I43" s="3" t="inlineStr"/>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>api|negative|security|state</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>API-REG-043</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>API — Регистрация, восстановление пароля, публичная лента</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Гейтинг непроверенных (verification_status)</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>PENDING ТК-админ не может подать оффер → 403 verification-required</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>Самозарегистрированная ТК (PENDING); токен ТК-админа; на стенде есть открытый заказ в ленте /transport/feed.</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>1. GET /api/v1/transport/feed — убедиться, что лента доступна.
+2. POST /api/v1/transport/orders/{orderId}/offers с валидным телом.</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>Шаг 1: HTTP 200 (просмотр разрешён). Шаг 2: HTTP 403, code='error.verification-required' — до одобрения супер-админом ставки запрещены.</t>
+        </is>
+      </c>
+      <c r="H44" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I44" s="3" t="inlineStr"/>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>api|negative|state</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>API-REG-044</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>API — Регистрация, восстановление пароля, публичная лента</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>Гейтинг непроверенных (verification_status)</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>PENDING ТК-админ: управление водителями/назначение/старт → 403</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>Самозарегистрированная ТК (PENDING), токен ТК-админа.</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>1. POST /api/v1/transport/drivers (создание водителя).
+2. POST /api/v1/transport/orders/{id}/drivers (привязка).
+3. POST /api/v1/transport/orders/{id}/start.</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>Каждый запрос: HTTP 403, code='error.verification-required' — все действия перевозчика (CRUD водителей, назначение, старт работ) закрыты до верификации; открыт только просмотр.</t>
+        </is>
+      </c>
+      <c r="H45" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I45" s="3" t="inlineStr"/>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>api|negative|state</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>API-REG-045</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>API — Регистрация, восстановление пароля, публичная лента</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Гейтинг непроверенных (verification_status)</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>REJECTED: действия остаются закрытыми → 403</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>Самозарегистрированный водитель ОТКЛОНЁН супер-админом (REJECTED).</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>1. POST /api/v1/driver/orders/{orderId}/offers под отклонённым водителем.
+2. GET /api/v1/me.</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>Шаг 1: HTTP 403, code='error.verification-required' — отклонённый приравнен к непроверенному, ставки недоступны. Шаг 2: HTTP 200, verificationStatus='REJECTED' — приложение может показать исход проверки.</t>
+        </is>
+      </c>
+      <c r="H46" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I46" s="3" t="inlineStr"/>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>api|negative|state</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>API-REG-046</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>API — Регистрация, восстановление пароля, публичная лента</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>Гейтинг непроверенных (verification_status)</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>Одобрение действует со следующего запроса, без перелогина</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>PENDING-водитель со «старым» accessToken (получен до одобрения). Токен SUPER_ADMIN.</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>1. Под PENDING-водителем убедиться: POST ставки → 403.
+2. Супер-админом одобрить: PATCH /api/v1/super-admin/transporters/{userId}/verification {status:'VERIFIED'}.
+3. НЕ перелогиниваясь, повторить POST ставки тем же accessToken водителя.</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>Шаг 3: ставка принимается (2xx) — статус читается из БД на каждом запросе, одобрение вступает в силу немедленно, старый токен остаётся действительным.</t>
+        </is>
+      </c>
+      <c r="H47" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I47" s="3" t="inlineStr"/>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>api|positive|state|session</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>API-REG-047</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>API — Регистрация, восстановление пароля, публичная лента</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>PATCH /api/v1/super-admin/transporters/{userId}/verification</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>Согласование перевозчика: PENDING → VERIFIED</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>Самозарегистрированный перевозчик (водитель или ТК-админ) в статусе PENDING; известен его userId. Токен SUPER_ADMIN.</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>1. PATCH /api/v1/super-admin/transporters/{userId}/verification с телом {status:'VERIFIED'}.
+2. GET /api/v1/me под перевозчиком.</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>Шаг 1: HTTP 204 без тела. Шаг 2: verificationStatus='VERIFIED' — аккаунт получает полный доступ (ставки разрешены). Пользователю уходит уведомление о смене статуса.</t>
+        </is>
+      </c>
+      <c r="H48" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I48" s="3" t="inlineStr"/>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>api|positive|lifecycle</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>API-REG-048</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>API — Регистрация, восстановление пароля, публичная лента</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>PATCH /api/v1/super-admin/transporters/{userId}/verification</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>Отклонение перевозчика: PENDING → REJECTED</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>Самозарегистрированный перевозчик в статусе PENDING. Токен SUPER_ADMIN.</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>1. PATCH .../verification с телом {status:'REJECTED', reason:'Документы не читаются'}.
+2. GET /api/v1/me под перевозчиком.</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>Шаг 1: HTTP 204. Шаг 2: verificationStatus='REJECTED'; гейтед-действия остаются 403 (см. API-REG-045). Поле reason опционально и не ломает запрос.</t>
+        </is>
+      </c>
+      <c r="H49" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I49" s="3" t="inlineStr"/>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>api|positive|lifecycle</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>API-REG-049</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>API — Регистрация, восстановление пароля, публичная лента</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>PATCH /api/v1/super-admin/transporters/{userId}/verification</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>Возврат в PENDING запрещён → 400</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>Любой перевозчик (хоть VERIFIED). Токен SUPER_ADMIN.</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>1. PATCH .../verification с телом {status:'PENDING'}.</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 400, code='error.verification.invalid-status', detail «Недопустимый статус» — решение проверки бывает только VERIFIED или REJECTED, обратно «на рассмотрение» аккаунт не возвращают.</t>
+        </is>
+      </c>
+      <c r="H50" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I50" s="3" t="inlineStr"/>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>api|negative|validation</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>API-REG-050</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>API — Регистрация, восстановление пароля, публичная лента</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>PATCH /api/v1/super-admin/transporters/{userId}/verification</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>Не-перевозчик (сотрудник отправителя, супер-админ) → 400</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>userId существующего пользователя роли SHIPPER_* или SUPER_ADMIN. Токен SUPER_ADMIN.</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>1. PATCH .../{userId}/verification с {status:'VERIFIED'} для этого userId.</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 400, code='error.verification.not-a-transporter', detail «Пользователь не является перевозчиком» — проверка применима только к TRANSPORT_ADMIN и DRIVER.</t>
+        </is>
+      </c>
+      <c r="H51" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I51" s="3" t="inlineStr"/>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>api|negative|validation</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>API-REG-051</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>API — Регистрация, восстановление пароля, публичная лента</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>PATCH /api/v1/super-admin/transporters/{userId}/verification</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>Несуществующий userId → 404</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>Токен SUPER_ADMIN.</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>1. PATCH .../transporters/&lt;случайный UUID&gt;/verification с {status:'VERIFIED'}.</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 404, code='error.employee.not-found'.</t>
+        </is>
+      </c>
+      <c r="H52" s="10" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="I52" s="3" t="inlineStr"/>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>api|negative</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>API-REG-052</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>API — Регистрация, восстановление пароля, публичная лента</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>PATCH /api/v1/super-admin/transporters/{userId}/verification</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>RBAC: решение о верификации доступно только SUPER_ADMIN</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>Токены TRANSPORT_ADMIN и SHIPPER_ADMIN; userId PENDING-перевозчика.</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>1. PATCH .../verification под TRANSPORT_ADMIN.
+2. PATCH под SHIPPER_ADMIN.
+3. PATCH вовсе без токена.</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>Шаги 1–2: HTTP 403 (нет роли SUPER_ADMIN) — перевозчик не может «одобрить сам себя». Шаг 3: HTTP 401. Статус пользователя не меняется.</t>
+        </is>
+      </c>
+      <c r="H53" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I53" s="3" t="inlineStr"/>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>api|negative|rbac|security</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>API-REG-053</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>API — Регистрация, восстановление пароля, публичная лента</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>GET /api/v1/super-admin/… (фильтр verificationStatus)</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>Фильтр по статусу проверки в списках водителей и ТК</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>На стенде есть перевозчики в статусах PENDING и VERIFIED. Токен SUPER_ADMIN.</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>1. GET /api/v1/super-admin/self-employed-drivers?verificationStatus=PENDING.
+2. GET /api/v1/super-admin/transport-companies?verificationStatus=PENDING.
+3. Повторить оба с verificationStatus=VERIFIED.</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>Каждый ответ HTTP 200; в выборке ТОЛЬКО записи запрошенного статуса (поле verificationStatus в каждой строке совпадает с фильтром). Без параметра возвращаются все.</t>
+        </is>
+      </c>
+      <c r="H54" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I54" s="3" t="inlineStr"/>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>api|positive|pagination</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>API-REG-054</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>API — Регистрация, восстановление пароля, публичная лента</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>POST /api/v1/auth/reset/otp</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>Запрос кода сброса для зарегистрированного телефона</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>Выделенный зарегистрированный пользователь (не трогать учётки основных прогонов — сброс отзывает сессии). Эндпойнт публичный.</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>1. POST /api/v1/auth/reset/otp с {phone:'&lt;телефон пользователя&gt;', lang:'ru'} без токена.</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200: challengeId (UUID) и resendAfter=45. Код уходит по SMS (на стенде с тестовым OTP-кодом — код фиксированный, SMS нет).</t>
+        </is>
+      </c>
+      <c r="H55" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I55" s="3" t="inlineStr"/>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>api|positive</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>API-REG-055</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>API — Регистрация, восстановление пароля, публичная лента</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>POST /api/v1/auth/reset/otp</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>Незарегистрированный телефон: ответ неотличим (нет утечки существования)</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>Заведомо незанятый телефон.</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>1. POST /api/v1/auth/reset/otp с этим телефоном.
+2. Сравнить форму ответа с ответом для зарегистрированного (API-REG-054).</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200 с теми же полями challengeId/resendAfter — НЕ 404 и не пустой ответ. По ответу нельзя определить, зарегистрирован ли номер (анти-перечисление аккаунтов): для чужого номера создаётся challenge-«пустышка».</t>
+        </is>
+      </c>
+      <c r="H56" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I56" s="3" t="inlineStr"/>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>api|positive|security</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>API-REG-056</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>API — Регистрация, восстановление пароля, публичная лента</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>POST /api/v1/auth/reset/otp/verify</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>Challenge-«пустышку» нельзя подтвердить даже тестовым кодом</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>challengeId получен для НЕзарегистрированного телефона (API-REG-055). Стенд в режиме тестового OTP-кода.</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>1. POST /api/v1/auth/reset/otp/verify с этим challengeId и тестовым кодом стенда.</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 422, code='error.otp.invalid' — код «пустышки» всегда случайный (даже в режиме тестового кода) и никуда не отправляется, поэтому подтвердить её нечем. Утечки существования нет и на шаге verify.</t>
+        </is>
+      </c>
+      <c r="H57" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I57" s="3" t="inlineStr"/>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>api|negative|security</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>API-REG-057</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>API — Регистрация, восстановление пароля, публичная лента</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>POST /api/v1/auth/reset/otp/verify</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>Верный код сброса → resetToken; механика попыток общая с регистрацией</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>Живой reset-challenge для зарегистрированного телефона; код известен.</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>1. POST verify с верным кодом.
+2. (Отдельным challenge) отправить неверный код, затем 5 неверных подряд.</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>Шаг 1: HTTP 200, в теле resetToken (JWT, живёт 15 минут). Шаг 2: неверный код → 422 error.otp.invalid; после 5 попыток → 429 error.otp.locked; истёкший код → 410 error.otp.expired; чужой/использованный challengeId → 401 error.otp.token-invalid — механика идентична регистрационной.</t>
+        </is>
+      </c>
+      <c r="H58" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I58" s="3" t="inlineStr"/>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>api|positive|negative</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>API-REG-058</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>API — Регистрация, восстановление пароля, публичная лента</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>POST /api/v1/auth/reset/complete</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>Установка нового пароля: вход по-новому работает, по-старому — нет</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>Действующий resetToken выделенного пользователя; старый пароль известен.</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>1. POST /api/v1/auth/reset/complete с {resetToken, password:'&lt;новый 6+&gt;'}.
+2. POST /api/v1/auth/login со СТАРЫМ паролем.
+3. POST /api/v1/auth/login с НОВЫМ паролем.</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>Шаг 1: HTTP 204 без тела. Шаг 2: HTTP 401, code='error.invalid-credentials'. Шаг 3: HTTP 200 с токенами.</t>
+        </is>
+      </c>
+      <c r="H59" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I59" s="3" t="inlineStr"/>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>api|positive|lifecycle</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>API-REG-059</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>API — Регистрация, восстановление пароля, публичная лента</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>POST /api/v1/auth/reset/complete</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>Сброс отзывает все сессии: старый refresh недействителен</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>Пользователь залогинен (refreshToken сохранён), затем выполнен сброс пароля (API-REG-058).</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>1. POST /api/v1/auth/refresh со СТАРЫМ refreshToken (полученным до сброса).</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 401 — при сбросе пароля отзываются все существующие сессии/refresh-токены: другие устройства обязаны войти заново с новым паролем.</t>
+        </is>
+      </c>
+      <c r="H60" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I60" s="3" t="inlineStr"/>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>api|negative|session|security</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>API-REG-060</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>API — Регистрация, восстановление пароля, публичная лента</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>POST /api/v1/auth/reset/complete</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>Повторное использование resetToken (replay) → 401</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>Сброс по токену уже выполнен.</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>1. Повторить POST /api/v1/auth/reset/complete с тем же resetToken и другим паролем.</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 401, code='error.otp.token-invalid' — токен одноразовый (challenge погашен при первом сбросе). Пароль повторно не меняется. Мусорный/просроченный (&gt;15 мин) resetToken — тот же 401.</t>
+        </is>
+      </c>
+      <c r="H61" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I61" s="3" t="inlineStr"/>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>api|negative|security|idempotency</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>API-REG-061</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>API — Регистрация, восстановление пароля, публичная лента</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>POST /api/v1/auth/reset/complete</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>Новый пароль короче 6 символов → 400, токен не сгорает</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>Действующий resetToken.</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>1. POST complete с password:'12345'.
+2. Повторить с валидным паролем (6+).</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>Шаг 1: HTTP 400, errors[] по полю password (validation.passwordMinLength). Шаг 2: HTTP 204 — ошибка валидации не расходует одноразовый токен.</t>
+        </is>
+      </c>
+      <c r="H62" s="10" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="I62" s="3" t="inlineStr"/>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>api|validation|boundary</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>API-REG-062</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>API — Регистрация, восстановление пароля, публичная лента</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>POST /api/v1/auth/reset/otp</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>Кулдаун 45 с и общий пер-IP лимит распространяются на сброс</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>Выделенный зарегистрированный телефон. Запускать серийно (общий лимит IP с register/otp).</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>1. Дважды подряд (быстрее 45 с) запросить POST /api/v1/auth/reset/otp на один телефон.</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>Второй запрос: HTTP 429, code='error.otp.resend-too-soon'. Пер-IP бюджет (20 OTP-запросов за 10 минут) общий для регистрации и сброса — при исчерпании 429 code='error.too-many-attempts'.</t>
+        </is>
+      </c>
+      <c r="H63" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I63" s="3" t="inlineStr"/>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>api|negative|ratelimit</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>API-REG-063</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>API — Регистрация, восстановление пароля, публичная лента</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>GET /api/v1/public/cargo</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>Гостевая лента грузов без токена: только открытые заказы, новые сверху</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>На стенде есть заказы в статусах PUBLISHED/QUOTED и хотя бы один в SELECTED/COMPLETED/CANCELLED.</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>1. GET /api/v1/public/cargo без заголовка Authorization.
+2. Сверить состав со списком заказов под авторизованной ролью.</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200, страничный ответ (по умолчанию 20 на страницу). В выборке ТОЛЬКО открытые заказы (опубликован/идёт сбор ставок); выбранные/в работе/завершённые/отменённые отсутствуют. Порядок — новые сверху.</t>
+        </is>
+      </c>
+      <c r="H64" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I64" s="3" t="inlineStr"/>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>api|positive</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>API-REG-064</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>API — Регистрация, восстановление пароля, публичная лента</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>GET /api/v1/public/cargo</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>Тизер не раскрывает чувствительных полей</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>В гостевой ленте есть заказы.</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>1. GET /api/v1/public/cargo и осмотреть JSON каждой записи.</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>В записи ровно: id (внутренний числовой), cargoType, loadDate, vehicleTypeName, driversCount, from/to (только регион). НЕТ: цен и ставок, названия/идентификаторов отправителя, номера заказа (displayNumber), адресов складов, заметок. Утечка любого из этих полей — баг безопасности.</t>
+        </is>
+      </c>
+      <c r="H65" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I65" s="3" t="inlineStr"/>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>api|positive|security</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>API-REG-065</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>API — Регистрация, восстановление пароля, публичная лента</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>GET /api/v1/public/cargo</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>Размер страницы каппится на 50</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>В ленте больше 50 открытых заказов (или проверить по полю size ответа).</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>1. GET /api/v1/public/cargo?size=100.</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200; фактический размер страницы в ответе — 50, не 100 (гостевой эндпойнт жёстче общего лимита). Ошибки нет — значение молча уменьшается.</t>
+        </is>
+      </c>
+      <c r="H66" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I66" s="3" t="inlineStr"/>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>api|boundary|pagination</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>API-REG-066</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>API — Регистрация, восстановление пароля, публичная лента</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>GET /api/v1/public/cargo</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>Клиентская сортировка игнорируется, а не падает</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>В ленте есть заказы.</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>1. GET /api/v1/public/cargo?sort=price,asc.
+2. GET /api/v1/public/cargo?sort=nonexistentField,desc.</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>Оба запроса HTTP 200 (не 400/500); порядок выдачи не меняется — всегда фиксированный «новые сверху». Гость не может прощупывать имена внутренних полей через ошибки сортировки.</t>
+        </is>
+      </c>
+      <c r="H67" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I67" s="3" t="inlineStr"/>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>api|negative|pagination|security</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>API-REG-067</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>API — Регистрация, восстановление пароля, публичная лента</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>GET /api/v1/public/cargo/{id}</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>Гостевая деталь: открытый заказ виден, закрытый и чужой id → 404</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>Известен id открытого заказа (из ленты) и id заказа в статусе SELECTED или позже.</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>1. GET /api/v1/public/cargo/{id открытого} без токена.
+2. GET /api/v1/public/cargo/{id закрытого}.
+3. GET /api/v1/public/cargo/999999999 (несуществующий).</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>Шаг 1: HTTP 200, те же нечувствительные поля тизера, что в ленте. Шаги 2–3: HTTP 404 — всё, что не PUBLISHED/QUOTED, для гостя неотличимо от несуществующего.</t>
+        </is>
+      </c>
+      <c r="H68" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I68" s="3" t="inlineStr"/>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>api|positive|negative|state</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="inlineStr">
+        <is>
+          <t>API-REG-068</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>API — Регистрация, восстановление пароля, публичная лента</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>GET /api/v1/public/cargo</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>Rate-limit гостевой ленты: свыше 60 запросов в минуту с IP → 429</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>Запускать серийно, отдельно от параллельных прогонов (лимит пер-IP, окно 1 минута; лента и деталь делят бюджет).</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>1. Выполнить с одного IP 60 запросов GET /api/v1/public/cargo за минуту.
+2. Выполнить 61-й запрос.</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>Первые 60 — HTTP 200. 61-й: HTTP 429 — защита от скрейпинга. Спустя минуту (скользящее окно) запросы снова проходят.</t>
+        </is>
+      </c>
+      <c r="H69" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I69" s="3" t="inlineStr"/>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>api|negative|ratelimit</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="inlineStr">
+        <is>
+          <t>API-REG-069</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>API — Регистрация, восстановление пароля, публичная лента</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>GET /api/v1/countries, /api/v1/cities (публично)</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>Справочники стран и городов доступны без токена (для формы регистрации ТК)</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>1. GET /api/v1/countries без заголовка Authorization.
+2. GET /api/v1/cities без токена.
+3. Контроль: POST/PATCH-справочники под /api/v1/super-admin/cities без токена.</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>Шаги 1–2: HTTP 200 со справочными данными (id, названия) — гость на шаге регистрации ТК выбирает города отправки до входа (MNZL-284). Шаг 3: HTTP 401 — публично только чтение GET, управление справочниками осталось под SUPER_ADMIN.</t>
+        </is>
+      </c>
+      <c r="H70" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I70" s="3" t="inlineStr"/>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>api|positive|security</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t>API-REG-070</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>API — Регистрация, восстановление пароля, публичная лента</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>GET /api/v1/public/cargo</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>permitAll не расползся: соседние эндпойнты без токена по-прежнему 401</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>1. Без токена: GET /api/v1/driver/feed.
+2. Без токена: GET /api/v1/transport/feed.
+3. Без токена: GET /api/v1/super-admin/transport-companies.</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>Все три: HTTP 401 — публичны только /api/v1/auth/**, /api/v1/public/** и GET-справочники countries/cities; остальные поверхности требуют Bearer-токен, как раньше.</t>
+        </is>
+      </c>
+      <c r="H71" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I71" s="3" t="inlineStr"/>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>api|negative|security|rbac</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/docs/testcases/manzil-api-testcases.xlsx
+++ b/docs/testcases/manzil-api-testcases.xlsx
@@ -53074,7 +53074,7 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>В записи ровно: id (внутренний числовой), cargoType, loadDate, vehicleTypeName, driversCount, from/to (только регион). НЕТ: цен и ставок, названия/идентификаторов отправителя, номера заказа (displayNumber), адресов складов, заметок. Утечка любого из этих полей — баг безопасности.</t>
+          <t>В записи ровно: id (внутренний числовой), cargoType, loadDate, vehicleTypeName, driversCount, from/to — каждый как {cityName, country} (город и страна, без точного адреса/склада). НЕТ: цен и ставок, названия/идентификаторов отправителя, номера заказа (displayNumber), адресов складов, заметок. Утечка любого из этих полей — баг безопасности.</t>
         </is>
       </c>
       <c r="H65" s="8" t="inlineStr">
@@ -53085,7 +53085,7 @@
       <c r="I65" s="3" t="inlineStr"/>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>api|positive|security</t>
+          <t>api|positive|security · уточнено по фактическому контракту 2026-07-24 (from/to={cityName,country})</t>
         </is>
       </c>
     </row>
